--- a/output/billing_report/ssc_dinas_vergleich.xlsx
+++ b/output/billing_report/ssc_dinas_vergleich.xlsx
@@ -125,10 +125,10 @@
     <xf numFmtId="165" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -137,10 +137,10 @@
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -149,10 +149,10 @@
     <xf numFmtId="165" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -520,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y35"/>
+  <dimension ref="A1:AC35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -534,20 +534,24 @@
     <col width="11" customWidth="1" min="9" max="9"/>
     <col width="8" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
     <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="9" customWidth="1" min="14" max="14"/>
-    <col width="10" customWidth="1" min="15" max="15"/>
-    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="9" customWidth="1" min="15" max="15"/>
+    <col width="9" customWidth="1" min="16" max="16"/>
     <col width="9" customWidth="1" min="17" max="17"/>
     <col width="9" customWidth="1" min="18" max="18"/>
-    <col width="9" customWidth="1" min="19" max="19"/>
-    <col width="9" customWidth="1" min="20" max="20"/>
+    <col width="10" customWidth="1" min="19" max="19"/>
+    <col width="10" customWidth="1" min="20" max="20"/>
     <col width="9" customWidth="1" min="21" max="21"/>
     <col width="9" customWidth="1" min="22" max="22"/>
     <col width="9" customWidth="1" min="23" max="23"/>
-    <col width="11" customWidth="1" min="24" max="24"/>
-    <col width="22" customWidth="1" min="25" max="25"/>
+    <col width="9" customWidth="1" min="24" max="24"/>
+    <col width="9" customWidth="1" min="25" max="25"/>
+    <col width="9" customWidth="1" min="26" max="26"/>
+    <col width="9" customWidth="1" min="27" max="27"/>
+    <col width="11" customWidth="1" min="28" max="28"/>
+    <col width="22" customWidth="1" min="29" max="29"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
@@ -615,70 +619,90 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
+          <t>Basis Menge</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
           <t>Basispreis</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>Eff. Preis</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>Tonnage kg</t>
         </is>
       </c>
-      <c r="O2" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>Stellplätze</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>Lademeter</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>Volumen</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
         <is>
           <t>Soll EUR</t>
         </is>
       </c>
-      <c r="P2" s="2" t="inlineStr">
+      <c r="T2" s="2" t="inlineStr">
         <is>
           <t>Fracht EUR</t>
         </is>
       </c>
-      <c r="Q2" s="2" t="inlineStr">
+      <c r="U2" s="2" t="inlineStr">
         <is>
           <t>Diesel EUR</t>
         </is>
       </c>
-      <c r="R2" s="2" t="inlineStr">
+      <c r="V2" s="2" t="inlineStr">
         <is>
           <t>Maut EUR</t>
         </is>
       </c>
-      <c r="S2" s="2" t="inlineStr">
+      <c r="W2" s="2" t="inlineStr">
         <is>
           <t>Lademittel</t>
         </is>
       </c>
-      <c r="T2" s="2" t="inlineStr">
+      <c r="X2" s="2" t="inlineStr">
         <is>
           <t>Peak EUR</t>
         </is>
       </c>
-      <c r="U2" s="2" t="inlineStr">
+      <c r="Y2" s="2" t="inlineStr">
         <is>
           <t>Neben EUR</t>
         </is>
       </c>
-      <c r="V2" s="2" t="inlineStr">
+      <c r="Z2" s="2" t="inlineStr">
         <is>
           <t>EUST Zoll</t>
         </is>
       </c>
-      <c r="W2" s="2" t="inlineStr">
+      <c r="AA2" s="2" t="inlineStr">
         <is>
           <t>Versich.</t>
         </is>
       </c>
-      <c r="X2" s="2" t="inlineStr">
+      <c r="AB2" s="2" t="inlineStr">
         <is>
           <t>Erlöse</t>
         </is>
       </c>
-      <c r="Y2" s="2" t="inlineStr">
+      <c r="AC2" s="2" t="inlineStr">
         <is>
           <t>Abw. Grund</t>
         </is>
@@ -746,45 +770,53 @@
         </is>
       </c>
       <c r="L4" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" s="7" t="n">
         <v>202.68</v>
       </c>
-      <c r="M4" s="6" t="n">
+      <c r="N4" s="7" t="n">
         <v>2712.35</v>
       </c>
-      <c r="N4" s="7" t="n">
-        <v>1</v>
-      </c>
       <c r="O4" s="6" t="n">
+        <v>22847</v>
+      </c>
+      <c r="P4" s="6" t="n"/>
+      <c r="Q4" s="6" t="n"/>
+      <c r="R4" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" s="7" t="n">
         <v>202.68</v>
       </c>
-      <c r="P4" s="6" t="n">
+      <c r="T4" s="7" t="n">
         <v>2712.35</v>
       </c>
-      <c r="Q4" s="6" t="n">
+      <c r="U4" s="7" t="n">
         <v>122.06</v>
       </c>
-      <c r="R4" s="6" t="n">
+      <c r="V4" s="7" t="n">
         <v>83</v>
       </c>
-      <c r="S4" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" s="6" t="n">
+      <c r="W4" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="7" t="n">
         <v>45</v>
       </c>
-      <c r="V4" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" s="6" t="n">
+      <c r="Z4" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="7" t="n">
         <v>2962.41</v>
       </c>
-      <c r="Y4" s="4" t="inlineStr">
+      <c r="AC4" s="4" t="inlineStr">
         <is>
           <t>Überfakturierung</t>
         </is>
@@ -845,45 +877,53 @@
         </is>
       </c>
       <c r="L5" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" s="11" t="n">
         <v>202.68</v>
       </c>
-      <c r="M5" s="10" t="n">
+      <c r="N5" s="11" t="n">
         <v>2712.35</v>
       </c>
-      <c r="N5" s="11" t="n">
-        <v>1</v>
-      </c>
       <c r="O5" s="10" t="n">
+        <v>17899</v>
+      </c>
+      <c r="P5" s="10" t="n"/>
+      <c r="Q5" s="10" t="n"/>
+      <c r="R5" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="11" t="n">
         <v>202.68</v>
       </c>
-      <c r="P5" s="10" t="n">
+      <c r="T5" s="11" t="n">
         <v>2712.35</v>
       </c>
-      <c r="Q5" s="10" t="n">
+      <c r="U5" s="11" t="n">
         <v>122.06</v>
       </c>
-      <c r="R5" s="10" t="n">
+      <c r="V5" s="11" t="n">
         <v>83</v>
       </c>
-      <c r="S5" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" s="10" t="n">
+      <c r="W5" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="11" t="n">
         <v>45</v>
       </c>
-      <c r="V5" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" s="10" t="n">
+      <c r="Z5" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="X5" s="10" t="n">
+      <c r="AB5" s="11" t="n">
         <v>2992.41</v>
       </c>
-      <c r="Y5" s="8" t="inlineStr">
+      <c r="AC5" s="8" t="inlineStr">
         <is>
           <t>Überfakturierung</t>
         </is>
@@ -944,45 +984,53 @@
         </is>
       </c>
       <c r="L6" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" s="11" t="n">
         <v>202.68</v>
       </c>
-      <c r="M6" s="10" t="n">
+      <c r="N6" s="11" t="n">
         <v>2712.35</v>
       </c>
-      <c r="N6" s="11" t="n">
-        <v>1</v>
-      </c>
       <c r="O6" s="10" t="n">
+        <v>23266</v>
+      </c>
+      <c r="P6" s="10" t="n"/>
+      <c r="Q6" s="10" t="n"/>
+      <c r="R6" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="11" t="n">
         <v>202.68</v>
       </c>
-      <c r="P6" s="10" t="n">
+      <c r="T6" s="11" t="n">
         <v>2712.35</v>
       </c>
-      <c r="Q6" s="10" t="n">
+      <c r="U6" s="11" t="n">
         <v>122.06</v>
       </c>
-      <c r="R6" s="10" t="n">
+      <c r="V6" s="11" t="n">
         <v>83</v>
       </c>
-      <c r="S6" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" s="10" t="n">
+      <c r="W6" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="11" t="n">
         <v>45</v>
       </c>
-      <c r="V6" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" s="10" t="n">
+      <c r="Z6" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="X6" s="10" t="n">
+      <c r="AB6" s="11" t="n">
         <v>2992.41</v>
       </c>
-      <c r="Y6" s="8" t="inlineStr">
+      <c r="AC6" s="8" t="inlineStr">
         <is>
           <t>Überfakturierung</t>
         </is>
@@ -1043,45 +1091,53 @@
         </is>
       </c>
       <c r="L7" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" s="11" t="n">
         <v>202.68</v>
       </c>
-      <c r="M7" s="10" t="n">
+      <c r="N7" s="11" t="n">
         <v>2712.35</v>
       </c>
-      <c r="N7" s="11" t="n">
-        <v>1</v>
-      </c>
       <c r="O7" s="10" t="n">
+        <v>21213</v>
+      </c>
+      <c r="P7" s="10" t="n"/>
+      <c r="Q7" s="10" t="n"/>
+      <c r="R7" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" s="11" t="n">
         <v>202.68</v>
       </c>
-      <c r="P7" s="10" t="n">
+      <c r="T7" s="11" t="n">
         <v>2712.35</v>
       </c>
-      <c r="Q7" s="10" t="n">
+      <c r="U7" s="11" t="n">
         <v>122.06</v>
       </c>
-      <c r="R7" s="10" t="n">
+      <c r="V7" s="11" t="n">
         <v>83</v>
       </c>
-      <c r="S7" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" s="10" t="n">
+      <c r="W7" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="11" t="n">
         <v>45</v>
       </c>
-      <c r="V7" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W7" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" s="10" t="n">
+      <c r="Z7" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="11" t="n">
         <v>2962.41</v>
       </c>
-      <c r="Y7" s="8" t="inlineStr">
+      <c r="AC7" s="8" t="inlineStr">
         <is>
           <t>Überfakturierung</t>
         </is>
@@ -1142,45 +1198,53 @@
         </is>
       </c>
       <c r="L8" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" s="11" t="n">
         <v>202.68</v>
       </c>
-      <c r="M8" s="10" t="n">
+      <c r="N8" s="11" t="n">
         <v>2712.35</v>
       </c>
-      <c r="N8" s="11" t="n">
-        <v>1</v>
-      </c>
       <c r="O8" s="10" t="n">
+        <v>22675</v>
+      </c>
+      <c r="P8" s="10" t="n"/>
+      <c r="Q8" s="10" t="n"/>
+      <c r="R8" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" s="11" t="n">
         <v>202.68</v>
       </c>
-      <c r="P8" s="10" t="n">
+      <c r="T8" s="11" t="n">
         <v>2712.35</v>
       </c>
-      <c r="Q8" s="10" t="n">
+      <c r="U8" s="11" t="n">
         <v>122.06</v>
       </c>
-      <c r="R8" s="10" t="n">
+      <c r="V8" s="11" t="n">
         <v>83</v>
       </c>
-      <c r="S8" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" s="10" t="n">
+      <c r="W8" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="11" t="n">
         <v>45</v>
       </c>
-      <c r="V8" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" s="10" t="n">
+      <c r="Z8" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="11" t="n">
         <v>2962.41</v>
       </c>
-      <c r="Y8" s="8" t="inlineStr">
+      <c r="AC8" s="8" t="inlineStr">
         <is>
           <t>Überfakturierung</t>
         </is>
@@ -1241,41 +1305,51 @@
         </is>
       </c>
       <c r="L9" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" s="7" t="n">
         <v>202.68</v>
       </c>
-      <c r="M9" s="6" t="n">
-        <v>0</v>
-      </c>
       <c r="N9" s="7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O9" s="6" t="n">
+        <v>112</v>
+      </c>
+      <c r="P9" s="6" t="n"/>
+      <c r="Q9" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R9" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" s="7" t="n">
         <v>202.68</v>
       </c>
-      <c r="P9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" s="6" t="n"/>
-      <c r="U9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W9" s="6" t="n"/>
-      <c r="X9" s="6" t="n">
+      <c r="T9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" s="7" t="n"/>
+      <c r="Y9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="7" t="n"/>
+      <c r="AB9" s="7" t="n">
         <v>128.11</v>
       </c>
-      <c r="Y9" s="4" t="inlineStr">
+      <c r="AC9" s="4" t="inlineStr">
         <is>
           <t>Unterfakturierung</t>
         </is>
@@ -1343,45 +1417,53 @@
         </is>
       </c>
       <c r="L12" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" s="7" t="n">
         <v>132.66</v>
       </c>
-      <c r="M12" s="6" t="n">
+      <c r="N12" s="7" t="n">
         <v>1154.6</v>
       </c>
-      <c r="N12" s="7" t="n">
-        <v>1</v>
-      </c>
       <c r="O12" s="6" t="n">
+        <v>20714</v>
+      </c>
+      <c r="P12" s="6" t="n"/>
+      <c r="Q12" s="6" t="n"/>
+      <c r="R12" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" s="7" t="n">
         <v>132.66</v>
       </c>
-      <c r="P12" s="6" t="n">
+      <c r="T12" s="7" t="n">
         <v>1154.6</v>
       </c>
-      <c r="Q12" s="6" t="n">
+      <c r="U12" s="7" t="n">
         <v>51.96</v>
       </c>
-      <c r="R12" s="6" t="n">
+      <c r="V12" s="7" t="n">
         <v>56</v>
       </c>
-      <c r="S12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" s="6" t="n">
+      <c r="W12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" s="7" t="n">
         <v>95</v>
       </c>
-      <c r="X12" s="6" t="n">
+      <c r="AB12" s="7" t="n">
         <v>1357.56</v>
       </c>
-      <c r="Y12" s="4" t="inlineStr">
+      <c r="AC12" s="4" t="inlineStr">
         <is>
           <t>Überfakturierung</t>
         </is>
@@ -1442,45 +1524,53 @@
         </is>
       </c>
       <c r="L13" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" s="11" t="n">
         <v>132.66</v>
       </c>
-      <c r="M13" s="10" t="n">
+      <c r="N13" s="11" t="n">
         <v>1154.6</v>
       </c>
-      <c r="N13" s="11" t="n">
-        <v>1</v>
-      </c>
       <c r="O13" s="10" t="n">
+        <v>22570</v>
+      </c>
+      <c r="P13" s="10" t="n"/>
+      <c r="Q13" s="10" t="n"/>
+      <c r="R13" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" s="11" t="n">
         <v>132.66</v>
       </c>
-      <c r="P13" s="10" t="n">
+      <c r="T13" s="11" t="n">
         <v>1154.6</v>
       </c>
-      <c r="Q13" s="10" t="n">
+      <c r="U13" s="11" t="n">
         <v>51.96</v>
       </c>
-      <c r="R13" s="10" t="n">
+      <c r="V13" s="11" t="n">
         <v>56</v>
       </c>
-      <c r="S13" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" s="10" t="n">
+      <c r="W13" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="11" t="n">
         <v>95</v>
       </c>
-      <c r="X13" s="10" t="n">
+      <c r="AB13" s="11" t="n">
         <v>1357.56</v>
       </c>
-      <c r="Y13" s="8" t="inlineStr">
+      <c r="AC13" s="8" t="inlineStr">
         <is>
           <t>Überfakturierung</t>
         </is>
@@ -1541,45 +1631,55 @@
         </is>
       </c>
       <c r="L14" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="M14" s="11" t="n">
         <v>110.25</v>
       </c>
-      <c r="M14" s="10" t="n">
+      <c r="N14" s="11" t="n">
         <v>23.445</v>
       </c>
-      <c r="N14" s="11" t="n">
-        <v>2</v>
-      </c>
       <c r="O14" s="10" t="n">
+        <v>484</v>
+      </c>
+      <c r="P14" s="10" t="n"/>
+      <c r="Q14" s="10" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="R14" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" s="11" t="n">
         <v>220.5</v>
       </c>
-      <c r="P14" s="10" t="n">
+      <c r="T14" s="11" t="n">
         <v>46.89</v>
       </c>
-      <c r="Q14" s="10" t="n">
+      <c r="U14" s="11" t="n">
         <v>1.06</v>
       </c>
-      <c r="R14" s="10" t="n">
+      <c r="V14" s="11" t="n">
         <v>0.89</v>
       </c>
-      <c r="S14" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T14" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U14" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W14" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" s="10" t="n">
+      <c r="W14" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="11" t="n">
         <v>48.84</v>
       </c>
-      <c r="Y14" s="8" t="inlineStr">
+      <c r="AC14" s="8" t="inlineStr">
         <is>
           <t>Unterfakturierung</t>
         </is>
@@ -1640,45 +1740,53 @@
         </is>
       </c>
       <c r="L15" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" s="11" t="n">
         <v>132.66</v>
       </c>
-      <c r="M15" s="10" t="n">
+      <c r="N15" s="11" t="n">
         <v>1154.6</v>
       </c>
-      <c r="N15" s="11" t="n">
-        <v>1</v>
-      </c>
       <c r="O15" s="10" t="n">
+        <v>21521</v>
+      </c>
+      <c r="P15" s="10" t="n"/>
+      <c r="Q15" s="10" t="n"/>
+      <c r="R15" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" s="11" t="n">
         <v>132.66</v>
       </c>
-      <c r="P15" s="10" t="n">
+      <c r="T15" s="11" t="n">
         <v>1154.6</v>
       </c>
-      <c r="Q15" s="10" t="n">
+      <c r="U15" s="11" t="n">
         <v>51.96</v>
       </c>
-      <c r="R15" s="10" t="n">
+      <c r="V15" s="11" t="n">
         <v>56</v>
       </c>
-      <c r="S15" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W15" s="10" t="n">
+      <c r="W15" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" s="11" t="n">
         <v>95</v>
       </c>
-      <c r="X15" s="10" t="n">
+      <c r="AB15" s="11" t="n">
         <v>1357.56</v>
       </c>
-      <c r="Y15" s="8" t="inlineStr">
+      <c r="AC15" s="8" t="inlineStr">
         <is>
           <t>Überfakturierung</t>
         </is>
@@ -1739,45 +1847,53 @@
         </is>
       </c>
       <c r="L16" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" s="11" t="n">
         <v>132.66</v>
       </c>
-      <c r="M16" s="10" t="n">
+      <c r="N16" s="11" t="n">
         <v>1154.6</v>
       </c>
-      <c r="N16" s="11" t="n">
-        <v>1</v>
-      </c>
       <c r="O16" s="10" t="n">
+        <v>21190</v>
+      </c>
+      <c r="P16" s="10" t="n"/>
+      <c r="Q16" s="10" t="n"/>
+      <c r="R16" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" s="11" t="n">
         <v>132.66</v>
       </c>
-      <c r="P16" s="10" t="n">
+      <c r="T16" s="11" t="n">
         <v>1154.6</v>
       </c>
-      <c r="Q16" s="10" t="n">
+      <c r="U16" s="11" t="n">
         <v>51.96</v>
       </c>
-      <c r="R16" s="10" t="n">
+      <c r="V16" s="11" t="n">
         <v>56</v>
       </c>
-      <c r="S16" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T16" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U16" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" s="10" t="n">
+      <c r="W16" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" s="11" t="n">
         <v>1262.56</v>
       </c>
-      <c r="Y16" s="8" t="inlineStr">
+      <c r="AC16" s="8" t="inlineStr">
         <is>
           <t>Überfakturierung</t>
         </is>
@@ -1838,45 +1954,57 @@
         </is>
       </c>
       <c r="L17" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" s="7" t="n">
         <v>132.66</v>
       </c>
-      <c r="M17" s="6" t="n">
+      <c r="N17" s="7" t="n">
         <v>132.66</v>
       </c>
-      <c r="N17" s="7" t="n">
+      <c r="O17" s="6" t="n">
+        <v>110</v>
+      </c>
+      <c r="P17" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="O17" s="6" t="n">
+      <c r="Q17" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R17" s="6" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="S17" s="7" t="n">
         <v>132.66</v>
       </c>
-      <c r="P17" s="6" t="n">
+      <c r="T17" s="7" t="n">
         <v>132.66</v>
       </c>
-      <c r="Q17" s="6" t="n">
+      <c r="U17" s="7" t="n">
         <v>2.48</v>
       </c>
-      <c r="R17" s="6" t="n">
+      <c r="V17" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="S17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" s="6" t="n">
+      <c r="W17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" s="7" t="n">
         <v>137.14</v>
       </c>
-      <c r="Y17" s="4" t="inlineStr">
+      <c r="AC17" s="4" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -1943,42 +2071,52 @@
           <t>EUR/Stpl</t>
         </is>
       </c>
-      <c r="L20" s="6" t="n"/>
-      <c r="M20" s="6" t="n">
+      <c r="L20" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="M20" s="7" t="n"/>
+      <c r="N20" s="7" t="n">
         <v>108.3333333333333</v>
       </c>
-      <c r="N20" s="7" t="n">
-        <v>24</v>
-      </c>
-      <c r="O20" s="6" t="n"/>
-      <c r="P20" s="6" t="n">
+      <c r="O20" s="6" t="n">
+        <v>14088</v>
+      </c>
+      <c r="P20" s="6" t="n"/>
+      <c r="Q20" s="6" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="R20" s="6" t="n">
+        <v>23.04</v>
+      </c>
+      <c r="S20" s="7" t="n"/>
+      <c r="T20" s="7" t="n">
         <v>2600</v>
       </c>
-      <c r="Q20" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W20" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" s="6" t="n">
+      <c r="U20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="7" t="n">
         <v>2600</v>
       </c>
-      <c r="Y20" s="4" t="inlineStr">
+      <c r="AC20" s="4" t="inlineStr">
         <is>
           <t>Soll n/a</t>
         </is>
@@ -2038,42 +2176,54 @@
           <t>EUR/Stpl</t>
         </is>
       </c>
-      <c r="L21" s="6" t="n"/>
-      <c r="M21" s="6" t="n">
+      <c r="L21" s="6" t="n">
+        <v>24</v>
+      </c>
+      <c r="M21" s="7" t="n"/>
+      <c r="N21" s="7" t="n">
         <v>84.3850875</v>
       </c>
-      <c r="N21" s="7" t="n">
+      <c r="O21" s="6" t="n">
+        <v>14088</v>
+      </c>
+      <c r="P21" s="6" t="n">
         <v>24</v>
       </c>
-      <c r="O21" s="6" t="n"/>
-      <c r="P21" s="6" t="n">
+      <c r="Q21" s="6" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="R21" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" s="7" t="n"/>
+      <c r="T21" s="7" t="n">
         <v>2025.2421</v>
       </c>
-      <c r="Q21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X21" s="6" t="n">
+      <c r="U21" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB21" s="7" t="n">
         <v>2025.2421</v>
       </c>
-      <c r="Y21" s="4" t="inlineStr">
+      <c r="AC21" s="4" t="inlineStr">
         <is>
           <t>Soll n/a</t>
         </is>
@@ -2140,42 +2290,52 @@
           <t>EUR/Stpl</t>
         </is>
       </c>
-      <c r="L24" s="10" t="n"/>
-      <c r="M24" s="10" t="n">
+      <c r="L24" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="M24" s="11" t="n"/>
+      <c r="N24" s="11" t="n">
         <v>168.75</v>
       </c>
-      <c r="N24" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="O24" s="10" t="n"/>
-      <c r="P24" s="10" t="n">
+      <c r="O24" s="10" t="n">
+        <v>1188</v>
+      </c>
+      <c r="P24" s="10" t="n"/>
+      <c r="Q24" s="10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R24" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" s="11" t="n"/>
+      <c r="T24" s="11" t="n">
         <v>675</v>
       </c>
-      <c r="Q24" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U24" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W24" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X24" s="10" t="n">
+      <c r="U24" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB24" s="11" t="n">
         <v>675</v>
       </c>
-      <c r="Y24" s="8" t="inlineStr">
+      <c r="AC24" s="8" t="inlineStr">
         <is>
           <t>Soll n/a</t>
         </is>
@@ -2235,42 +2395,52 @@
           <t>EUR/Stpl</t>
         </is>
       </c>
-      <c r="L25" s="6" t="n"/>
-      <c r="M25" s="6" t="n">
+      <c r="L25" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="M25" s="7" t="n"/>
+      <c r="N25" s="7" t="n">
         <v>168.75</v>
       </c>
-      <c r="N25" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="O25" s="6" t="n"/>
-      <c r="P25" s="6" t="n">
+      <c r="O25" s="6" t="n">
+        <v>1122</v>
+      </c>
+      <c r="P25" s="6" t="n"/>
+      <c r="Q25" s="6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R25" s="6" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="S25" s="7" t="n"/>
+      <c r="T25" s="7" t="n">
         <v>506.25</v>
       </c>
-      <c r="Q25" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U25" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W25" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X25" s="6" t="n">
+      <c r="U25" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA25" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB25" s="7" t="n">
         <v>506.25</v>
       </c>
-      <c r="Y25" s="4" t="inlineStr">
+      <c r="AC25" s="4" t="inlineStr">
         <is>
           <t>Soll n/a</t>
         </is>
@@ -2330,42 +2500,54 @@
           <t>EUR/Stpl</t>
         </is>
       </c>
-      <c r="L26" s="6" t="n"/>
-      <c r="M26" s="6" t="n">
+      <c r="L26" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="M26" s="7" t="n"/>
+      <c r="N26" s="7" t="n">
         <v>50.60263333333333</v>
       </c>
-      <c r="N26" s="7" t="n">
+      <c r="O26" s="6" t="n">
+        <v>1056</v>
+      </c>
+      <c r="P26" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="O26" s="6" t="n"/>
-      <c r="P26" s="6" t="n">
+      <c r="Q26" s="6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R26" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" s="7" t="n"/>
+      <c r="T26" s="7" t="n">
         <v>151.8079</v>
       </c>
-      <c r="Q26" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U26" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W26" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X26" s="6" t="n">
+      <c r="U26" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z26" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB26" s="7" t="n">
         <v>151.8079</v>
       </c>
-      <c r="Y26" s="4" t="inlineStr">
+      <c r="AC26" s="4" t="inlineStr">
         <is>
           <t>Soll n/a</t>
         </is>
@@ -2432,42 +2614,52 @@
           <t>EUR/Stpl</t>
         </is>
       </c>
-      <c r="L29" s="6" t="n"/>
-      <c r="M29" s="6" t="n">
+      <c r="L29" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M29" s="7" t="n"/>
+      <c r="N29" s="7" t="n">
         <v>121.53</v>
       </c>
-      <c r="N29" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="O29" s="6" t="n"/>
-      <c r="P29" s="6" t="n">
+      <c r="O29" s="6" t="n">
+        <v>669</v>
+      </c>
+      <c r="P29" s="6" t="n"/>
+      <c r="Q29" s="6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R29" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" s="7" t="n"/>
+      <c r="T29" s="7" t="n">
         <v>121.53</v>
       </c>
-      <c r="Q29" s="6" t="n">
+      <c r="U29" s="7" t="n">
         <v>2.73</v>
       </c>
-      <c r="R29" s="6" t="n">
+      <c r="V29" s="7" t="n">
         <v>2.48</v>
       </c>
-      <c r="S29" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U29" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W29" s="6" t="n">
+      <c r="W29" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="7" t="n">
         <v>1.82</v>
       </c>
-      <c r="X29" s="6" t="n">
+      <c r="AB29" s="7" t="n">
         <v>128.56</v>
       </c>
-      <c r="Y29" s="4" t="inlineStr">
+      <c r="AC29" s="4" t="inlineStr">
         <is>
           <t>Soll n/a</t>
         </is>
@@ -2527,42 +2719,50 @@
           <t>EUR/Stpl</t>
         </is>
       </c>
-      <c r="L30" s="10" t="n"/>
-      <c r="M30" s="10" t="n">
+      <c r="L30" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M30" s="11" t="n"/>
+      <c r="N30" s="11" t="n">
         <v>3706.45</v>
       </c>
-      <c r="N30" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O30" s="10" t="n"/>
-      <c r="P30" s="10" t="n">
+      <c r="O30" s="10" t="n">
+        <v>22681</v>
+      </c>
+      <c r="P30" s="10" t="n"/>
+      <c r="Q30" s="10" t="n"/>
+      <c r="R30" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" s="11" t="n"/>
+      <c r="T30" s="11" t="n">
         <v>3706.45</v>
       </c>
-      <c r="Q30" s="10" t="n">
+      <c r="U30" s="11" t="n">
         <v>166.79</v>
       </c>
-      <c r="R30" s="10" t="n">
+      <c r="V30" s="11" t="n">
         <v>68</v>
       </c>
-      <c r="S30" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U30" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W30" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X30" s="10" t="n">
+      <c r="W30" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z30" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA30" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB30" s="11" t="n">
         <v>3941.24</v>
       </c>
-      <c r="Y30" s="8" t="inlineStr">
+      <c r="AC30" s="8" t="inlineStr">
         <is>
           <t>Soll n/a</t>
         </is>
@@ -2622,42 +2822,52 @@
           <t>EUR/Stpl</t>
         </is>
       </c>
-      <c r="L31" s="10" t="n"/>
-      <c r="M31" s="10" t="n">
+      <c r="L31" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M31" s="11" t="n"/>
+      <c r="N31" s="11" t="n">
         <v>127.07</v>
       </c>
-      <c r="N31" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O31" s="10" t="n"/>
-      <c r="P31" s="10" t="n">
+      <c r="O31" s="10" t="n">
+        <v>472</v>
+      </c>
+      <c r="P31" s="10" t="n"/>
+      <c r="Q31" s="10" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R31" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" s="11" t="n"/>
+      <c r="T31" s="11" t="n">
         <v>127.07</v>
       </c>
-      <c r="Q31" s="10" t="n">
+      <c r="U31" s="11" t="n">
         <v>2.86</v>
       </c>
-      <c r="R31" s="10" t="n">
+      <c r="V31" s="11" t="n">
         <v>2.4</v>
       </c>
-      <c r="S31" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U31" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W31" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X31" s="10" t="n">
+      <c r="W31" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z31" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA31" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB31" s="11" t="n">
         <v>132.33</v>
       </c>
-      <c r="Y31" s="8" t="inlineStr">
+      <c r="AC31" s="8" t="inlineStr">
         <is>
           <t>Soll n/a</t>
         </is>
@@ -2717,42 +2927,50 @@
           <t>EUR/Stpl</t>
         </is>
       </c>
-      <c r="L32" s="10" t="n"/>
-      <c r="M32" s="10" t="n">
+      <c r="L32" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M32" s="11" t="n"/>
+      <c r="N32" s="11" t="n">
         <v>3706.45</v>
       </c>
-      <c r="N32" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O32" s="10" t="n"/>
-      <c r="P32" s="10" t="n">
+      <c r="O32" s="10" t="n">
+        <v>19971</v>
+      </c>
+      <c r="P32" s="10" t="n"/>
+      <c r="Q32" s="10" t="n"/>
+      <c r="R32" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" s="11" t="n"/>
+      <c r="T32" s="11" t="n">
         <v>3706.45</v>
       </c>
-      <c r="Q32" s="10" t="n">
+      <c r="U32" s="11" t="n">
         <v>166.79</v>
       </c>
-      <c r="R32" s="10" t="n">
+      <c r="V32" s="11" t="n">
         <v>68</v>
       </c>
-      <c r="S32" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T32" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U32" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W32" s="10" t="n">
+      <c r="W32" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="X32" s="10" t="n">
+      <c r="AB32" s="11" t="n">
         <v>3971.24</v>
       </c>
-      <c r="Y32" s="8" t="inlineStr">
+      <c r="AC32" s="8" t="inlineStr">
         <is>
           <t>Soll n/a</t>
         </is>
@@ -2812,42 +3030,50 @@
           <t>EUR/Stpl</t>
         </is>
       </c>
-      <c r="L33" s="10" t="n"/>
-      <c r="M33" s="10" t="n">
+      <c r="L33" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M33" s="11" t="n"/>
+      <c r="N33" s="11" t="n">
         <v>3706.45</v>
       </c>
-      <c r="N33" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="O33" s="10" t="n"/>
-      <c r="P33" s="10" t="n">
+      <c r="O33" s="10" t="n">
+        <v>13493</v>
+      </c>
+      <c r="P33" s="10" t="n"/>
+      <c r="Q33" s="10" t="n"/>
+      <c r="R33" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S33" s="11" t="n"/>
+      <c r="T33" s="11" t="n">
         <v>3706.45</v>
       </c>
-      <c r="Q33" s="10" t="n">
+      <c r="U33" s="11" t="n">
         <v>131.21</v>
       </c>
-      <c r="R33" s="10" t="n">
+      <c r="V33" s="11" t="n">
         <v>68</v>
       </c>
-      <c r="S33" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T33" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U33" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W33" s="10" t="n">
+      <c r="W33" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z33" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA33" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="X33" s="10" t="n">
+      <c r="AB33" s="11" t="n">
         <v>3935.66</v>
       </c>
-      <c r="Y33" s="8" t="inlineStr">
+      <c r="AC33" s="8" t="inlineStr">
         <is>
           <t>Soll n/a</t>
         </is>
@@ -2907,38 +3133,48 @@
           <t>EUR/Stpl</t>
         </is>
       </c>
-      <c r="L34" s="6" t="n"/>
-      <c r="M34" s="6" t="n">
-        <v>0</v>
-      </c>
+      <c r="L34" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M34" s="7" t="n"/>
       <c r="N34" s="7" t="n">
-        <v>1</v>
-      </c>
-      <c r="O34" s="6" t="n"/>
-      <c r="P34" s="6" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O34" s="6" t="n">
+        <v>3768</v>
+      </c>
+      <c r="P34" s="6" t="n"/>
       <c r="Q34" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R34" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="S34" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T34" s="6" t="n"/>
-      <c r="U34" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V34" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W34" s="6" t="n"/>
-      <c r="X34" s="6" t="n">
+      <c r="S34" s="7" t="n"/>
+      <c r="T34" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" s="7" t="n"/>
+      <c r="Y34" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z34" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA34" s="7" t="n"/>
+      <c r="AB34" s="7" t="n">
         <v>778.1</v>
       </c>
-      <c r="Y34" s="4" t="inlineStr">
+      <c r="AC34" s="4" t="inlineStr">
         <is>
           <t>Soll n/a</t>
         </is>
@@ -2998,38 +3234,46 @@
           <t>EUR/Stpl</t>
         </is>
       </c>
-      <c r="L35" s="14" t="n"/>
-      <c r="M35" s="14" t="n">
-        <v>0</v>
-      </c>
+      <c r="L35" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M35" s="15" t="n"/>
       <c r="N35" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="O35" s="14" t="n"/>
-      <c r="P35" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q35" s="14" t="n">
-        <v>0</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="O35" s="14" t="n">
+        <v>22094</v>
+      </c>
+      <c r="P35" s="14" t="n"/>
+      <c r="Q35" s="14" t="n"/>
       <c r="R35" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="S35" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="T35" s="14" t="n"/>
-      <c r="U35" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V35" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="W35" s="14" t="n"/>
-      <c r="X35" s="14" t="n">
+      <c r="S35" s="15" t="n"/>
+      <c r="T35" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" s="15" t="n"/>
+      <c r="Y35" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z35" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA35" s="15" t="n"/>
+      <c r="AB35" s="15" t="n">
         <v>3935.66</v>
       </c>
-      <c r="Y35" s="12" t="inlineStr">
+      <c r="AC35" s="12" t="inlineStr">
         <is>
           <t>Soll n/a</t>
         </is>
@@ -3037,12 +3281,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A19:Y19"/>
-    <mergeCell ref="A11:Y11"/>
-    <mergeCell ref="A28:Y28"/>
-    <mergeCell ref="A1:Y1"/>
-    <mergeCell ref="A23:Y23"/>
-    <mergeCell ref="A3:Y3"/>
+    <mergeCell ref="A19:AC19"/>
+    <mergeCell ref="A11:AC11"/>
+    <mergeCell ref="A1:AC1"/>
+    <mergeCell ref="A23:AC23"/>
+    <mergeCell ref="A3:AC3"/>
+    <mergeCell ref="A28:AC28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/billing_report/ssc_dinas_vergleich.xlsx
+++ b/output/billing_report/ssc_dinas_vergleich.xlsx
@@ -122,11 +122,11 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="165" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
@@ -134,11 +134,11 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
@@ -146,11 +146,11 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="165" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
@@ -520,38 +520,42 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC35"/>
+  <dimension ref="A1:AG35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="5" customWidth="1" min="6" max="6"/>
-    <col width="8" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
-    <col width="8" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="9" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="10" customWidth="1" min="14" max="14"/>
-    <col width="9" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="5" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="8" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
     <col width="9" customWidth="1" min="16" max="16"/>
-    <col width="9" customWidth="1" min="17" max="17"/>
-    <col width="9" customWidth="1" min="18" max="18"/>
-    <col width="10" customWidth="1" min="19" max="19"/>
-    <col width="10" customWidth="1" min="20" max="20"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="9" customWidth="1" min="19" max="19"/>
+    <col width="9" customWidth="1" min="20" max="20"/>
     <col width="9" customWidth="1" min="21" max="21"/>
     <col width="9" customWidth="1" min="22" max="22"/>
-    <col width="9" customWidth="1" min="23" max="23"/>
-    <col width="9" customWidth="1" min="24" max="24"/>
+    <col width="10" customWidth="1" min="23" max="23"/>
+    <col width="10" customWidth="1" min="24" max="24"/>
     <col width="9" customWidth="1" min="25" max="25"/>
     <col width="9" customWidth="1" min="26" max="26"/>
     <col width="9" customWidth="1" min="27" max="27"/>
-    <col width="11" customWidth="1" min="28" max="28"/>
-    <col width="22" customWidth="1" min="29" max="29"/>
+    <col width="9" customWidth="1" min="28" max="28"/>
+    <col width="9" customWidth="1" min="29" max="29"/>
+    <col width="9" customWidth="1" min="30" max="30"/>
+    <col width="9" customWidth="1" min="31" max="31"/>
+    <col width="11" customWidth="1" min="32" max="32"/>
+    <col width="22" customWidth="1" min="33" max="33"/>
   </cols>
   <sheetData>
     <row r="1" ht="20" customHeight="1">
@@ -574,135 +578,155 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>Master-Nr</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Sub-Nr(n)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Anzahl Subs</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Ist Master</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>Rech.-Nr</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>Sendungsdatum</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>Kunde</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>Land</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>Empf.PLZ</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>Vers.PLZ</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="M2" s="2" t="inlineStr">
         <is>
           <t>Gew.band</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="N2" s="2" t="inlineStr">
         <is>
           <t>Zone</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="O2" s="2" t="inlineStr">
         <is>
           <t>Basis</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr">
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>Basis Menge</t>
         </is>
       </c>
-      <c r="M2" s="2" t="inlineStr">
+      <c r="Q2" s="2" t="inlineStr">
         <is>
           <t>Basispreis</t>
         </is>
       </c>
-      <c r="N2" s="2" t="inlineStr">
+      <c r="R2" s="2" t="inlineStr">
         <is>
           <t>Eff. Preis</t>
         </is>
       </c>
-      <c r="O2" s="2" t="inlineStr">
+      <c r="S2" s="2" t="inlineStr">
         <is>
           <t>Tonnage kg</t>
         </is>
       </c>
-      <c r="P2" s="2" t="inlineStr">
+      <c r="T2" s="2" t="inlineStr">
         <is>
           <t>Stellplätze</t>
         </is>
       </c>
-      <c r="Q2" s="2" t="inlineStr">
+      <c r="U2" s="2" t="inlineStr">
         <is>
           <t>Lademeter</t>
         </is>
       </c>
-      <c r="R2" s="2" t="inlineStr">
+      <c r="V2" s="2" t="inlineStr">
         <is>
           <t>Volumen</t>
         </is>
       </c>
-      <c r="S2" s="2" t="inlineStr">
+      <c r="W2" s="2" t="inlineStr">
         <is>
           <t>Soll EUR</t>
         </is>
       </c>
-      <c r="T2" s="2" t="inlineStr">
+      <c r="X2" s="2" t="inlineStr">
         <is>
           <t>Fracht EUR</t>
         </is>
       </c>
-      <c r="U2" s="2" t="inlineStr">
+      <c r="Y2" s="2" t="inlineStr">
         <is>
           <t>Diesel EUR</t>
         </is>
       </c>
-      <c r="V2" s="2" t="inlineStr">
+      <c r="Z2" s="2" t="inlineStr">
         <is>
           <t>Maut EUR</t>
         </is>
       </c>
-      <c r="W2" s="2" t="inlineStr">
+      <c r="AA2" s="2" t="inlineStr">
         <is>
           <t>Lademittel</t>
         </is>
       </c>
-      <c r="X2" s="2" t="inlineStr">
+      <c r="AB2" s="2" t="inlineStr">
         <is>
           <t>Peak EUR</t>
         </is>
       </c>
-      <c r="Y2" s="2" t="inlineStr">
+      <c r="AC2" s="2" t="inlineStr">
         <is>
           <t>Neben EUR</t>
         </is>
       </c>
-      <c r="Z2" s="2" t="inlineStr">
+      <c r="AD2" s="2" t="inlineStr">
         <is>
           <t>EUST Zoll</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
+      <c r="AE2" s="2" t="inlineStr">
         <is>
           <t>Versich.</t>
         </is>
       </c>
-      <c r="AB2" s="2" t="inlineStr">
+      <c r="AF2" s="2" t="inlineStr">
         <is>
           <t>Erlöse</t>
         </is>
       </c>
-      <c r="AC2" s="2" t="inlineStr">
+      <c r="AG2" s="2" t="inlineStr">
         <is>
           <t>Abw. Grund</t>
         </is>
@@ -726,97 +750,103 @@
           <t>32883326</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="4" t="inlineStr"/>
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>3763117</t>
         </is>
       </c>
-      <c r="D4" s="5" t="n">
+      <c r="H4" s="6" t="n">
         <v>45772</v>
       </c>
-      <c r="E4" s="4" t="inlineStr">
+      <c r="I4" s="4" t="inlineStr">
         <is>
           <t>Sika Supply Center GmbH</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="J4" s="4" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="K4" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">LU5 5    </t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="L4" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">70499    </t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr">
+      <c r="M4" s="4" t="inlineStr">
         <is>
           <t>bis 2 Stpl</t>
         </is>
       </c>
-      <c r="J4" s="4" t="inlineStr">
+      <c r="N4" s="4" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="K4" s="4" t="inlineStr">
+      <c r="O4" s="4" t="inlineStr">
         <is>
           <t>EUR/Stpl</t>
         </is>
       </c>
-      <c r="L4" s="6" t="n">
+      <c r="P4" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="M4" s="7" t="n">
+      <c r="Q4" s="7" t="n">
         <v>202.68</v>
       </c>
-      <c r="N4" s="7" t="n">
+      <c r="R4" s="7" t="n">
         <v>2712.35</v>
       </c>
-      <c r="O4" s="6" t="n">
+      <c r="S4" s="5" t="n">
         <v>22847</v>
       </c>
-      <c r="P4" s="6" t="n"/>
-      <c r="Q4" s="6" t="n"/>
-      <c r="R4" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" s="7" t="n">
+      <c r="T4" s="5" t="n"/>
+      <c r="U4" s="5" t="n"/>
+      <c r="V4" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" s="7" t="n">
         <v>202.68</v>
       </c>
-      <c r="T4" s="7" t="n">
+      <c r="X4" s="7" t="n">
         <v>2712.35</v>
       </c>
-      <c r="U4" s="7" t="n">
+      <c r="Y4" s="7" t="n">
         <v>122.06</v>
       </c>
-      <c r="V4" s="7" t="n">
+      <c r="Z4" s="7" t="n">
         <v>83</v>
       </c>
-      <c r="W4" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y4" s="7" t="n">
+      <c r="AA4" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" s="7" t="n">
         <v>45</v>
       </c>
-      <c r="Z4" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA4" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB4" s="7" t="n">
+      <c r="AD4" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" s="7" t="n">
         <v>2962.41</v>
       </c>
-      <c r="AC4" s="4" t="inlineStr">
+      <c r="AG4" s="4" t="inlineStr">
         <is>
           <t>Überfakturierung</t>
         </is>
@@ -833,97 +863,103 @@
           <t>32885028</t>
         </is>
       </c>
-      <c r="C5" s="8" t="inlineStr">
+      <c r="C5" s="8" t="n"/>
+      <c r="D5" s="8" t="n"/>
+      <c r="E5" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="8" t="inlineStr"/>
+      <c r="G5" s="8" t="inlineStr">
         <is>
           <t>3763117</t>
         </is>
       </c>
-      <c r="D5" s="9" t="n">
+      <c r="H5" s="10" t="n">
         <v>45776</v>
       </c>
-      <c r="E5" s="8" t="inlineStr">
+      <c r="I5" s="8" t="inlineStr">
         <is>
           <t>Sika Supply Center GmbH</t>
         </is>
       </c>
-      <c r="F5" s="8" t="inlineStr">
+      <c r="J5" s="8" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="G5" s="8" t="inlineStr">
+      <c r="K5" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">LU5 5    </t>
         </is>
       </c>
-      <c r="H5" s="8" t="inlineStr">
+      <c r="L5" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">70499    </t>
         </is>
       </c>
-      <c r="I5" s="8" t="inlineStr">
+      <c r="M5" s="8" t="inlineStr">
         <is>
           <t>bis 2 Stpl</t>
         </is>
       </c>
-      <c r="J5" s="8" t="inlineStr">
+      <c r="N5" s="8" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="K5" s="8" t="inlineStr">
+      <c r="O5" s="8" t="inlineStr">
         <is>
           <t>EUR/Stpl</t>
         </is>
       </c>
-      <c r="L5" s="10" t="n">
+      <c r="P5" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="M5" s="11" t="n">
+      <c r="Q5" s="11" t="n">
         <v>202.68</v>
       </c>
-      <c r="N5" s="11" t="n">
+      <c r="R5" s="11" t="n">
         <v>2712.35</v>
       </c>
-      <c r="O5" s="10" t="n">
+      <c r="S5" s="9" t="n">
         <v>17899</v>
       </c>
-      <c r="P5" s="10" t="n"/>
-      <c r="Q5" s="10" t="n"/>
-      <c r="R5" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" s="11" t="n">
+      <c r="T5" s="9" t="n"/>
+      <c r="U5" s="9" t="n"/>
+      <c r="V5" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" s="11" t="n">
         <v>202.68</v>
       </c>
-      <c r="T5" s="11" t="n">
+      <c r="X5" s="11" t="n">
         <v>2712.35</v>
       </c>
-      <c r="U5" s="11" t="n">
+      <c r="Y5" s="11" t="n">
         <v>122.06</v>
       </c>
-      <c r="V5" s="11" t="n">
+      <c r="Z5" s="11" t="n">
         <v>83</v>
       </c>
-      <c r="W5" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y5" s="11" t="n">
+      <c r="AA5" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="11" t="n">
         <v>45</v>
       </c>
-      <c r="Z5" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA5" s="11" t="n">
+      <c r="AD5" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="AB5" s="11" t="n">
+      <c r="AF5" s="11" t="n">
         <v>2992.41</v>
       </c>
-      <c r="AC5" s="8" t="inlineStr">
+      <c r="AG5" s="8" t="inlineStr">
         <is>
           <t>Überfakturierung</t>
         </is>
@@ -940,97 +976,103 @@
           <t>32888172</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="8" t="n"/>
+      <c r="D6" s="8" t="n"/>
+      <c r="E6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="8" t="inlineStr"/>
+      <c r="G6" s="8" t="inlineStr">
         <is>
           <t>3767099</t>
         </is>
       </c>
-      <c r="D6" s="9" t="n">
+      <c r="H6" s="10" t="n">
         <v>45783</v>
       </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="I6" s="8" t="inlineStr">
         <is>
           <t>Sika Supply Center GmbH</t>
         </is>
       </c>
-      <c r="F6" s="8" t="inlineStr">
+      <c r="J6" s="8" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="G6" s="8" t="inlineStr">
+      <c r="K6" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">LU5 5    </t>
         </is>
       </c>
-      <c r="H6" s="8" t="inlineStr">
+      <c r="L6" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">70499    </t>
         </is>
       </c>
-      <c r="I6" s="8" t="inlineStr">
+      <c r="M6" s="8" t="inlineStr">
         <is>
           <t>bis 2 Stpl</t>
         </is>
       </c>
-      <c r="J6" s="8" t="inlineStr">
+      <c r="N6" s="8" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="K6" s="8" t="inlineStr">
+      <c r="O6" s="8" t="inlineStr">
         <is>
           <t>EUR/Stpl</t>
         </is>
       </c>
-      <c r="L6" s="10" t="n">
+      <c r="P6" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="M6" s="11" t="n">
+      <c r="Q6" s="11" t="n">
         <v>202.68</v>
       </c>
-      <c r="N6" s="11" t="n">
+      <c r="R6" s="11" t="n">
         <v>2712.35</v>
       </c>
-      <c r="O6" s="10" t="n">
+      <c r="S6" s="9" t="n">
         <v>23266</v>
       </c>
-      <c r="P6" s="10" t="n"/>
-      <c r="Q6" s="10" t="n"/>
-      <c r="R6" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" s="11" t="n">
+      <c r="T6" s="9" t="n"/>
+      <c r="U6" s="9" t="n"/>
+      <c r="V6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" s="11" t="n">
         <v>202.68</v>
       </c>
-      <c r="T6" s="11" t="n">
+      <c r="X6" s="11" t="n">
         <v>2712.35</v>
       </c>
-      <c r="U6" s="11" t="n">
+      <c r="Y6" s="11" t="n">
         <v>122.06</v>
       </c>
-      <c r="V6" s="11" t="n">
+      <c r="Z6" s="11" t="n">
         <v>83</v>
       </c>
-      <c r="W6" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y6" s="11" t="n">
+      <c r="AA6" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="11" t="n">
         <v>45</v>
       </c>
-      <c r="Z6" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA6" s="11" t="n">
+      <c r="AD6" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="AB6" s="11" t="n">
+      <c r="AF6" s="11" t="n">
         <v>2992.41</v>
       </c>
-      <c r="AC6" s="8" t="inlineStr">
+      <c r="AG6" s="8" t="inlineStr">
         <is>
           <t>Überfakturierung</t>
         </is>
@@ -1047,97 +1089,103 @@
           <t>32889605</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C7" s="8" t="n"/>
+      <c r="D7" s="8" t="n"/>
+      <c r="E7" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="8" t="inlineStr"/>
+      <c r="G7" s="8" t="inlineStr">
         <is>
           <t>3767099</t>
         </is>
       </c>
-      <c r="D7" s="9" t="n">
+      <c r="H7" s="10" t="n">
         <v>45785</v>
       </c>
-      <c r="E7" s="8" t="inlineStr">
+      <c r="I7" s="8" t="inlineStr">
         <is>
           <t>Sika Supply Center GmbH</t>
         </is>
       </c>
-      <c r="F7" s="8" t="inlineStr">
+      <c r="J7" s="8" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="G7" s="8" t="inlineStr">
+      <c r="K7" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">LU5 5    </t>
         </is>
       </c>
-      <c r="H7" s="8" t="inlineStr">
+      <c r="L7" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">70499    </t>
         </is>
       </c>
-      <c r="I7" s="8" t="inlineStr">
+      <c r="M7" s="8" t="inlineStr">
         <is>
           <t>bis 2 Stpl</t>
         </is>
       </c>
-      <c r="J7" s="8" t="inlineStr">
+      <c r="N7" s="8" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="K7" s="8" t="inlineStr">
+      <c r="O7" s="8" t="inlineStr">
         <is>
           <t>EUR/Stpl</t>
         </is>
       </c>
-      <c r="L7" s="10" t="n">
+      <c r="P7" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="M7" s="11" t="n">
+      <c r="Q7" s="11" t="n">
         <v>202.68</v>
       </c>
-      <c r="N7" s="11" t="n">
+      <c r="R7" s="11" t="n">
         <v>2712.35</v>
       </c>
-      <c r="O7" s="10" t="n">
+      <c r="S7" s="9" t="n">
         <v>21213</v>
       </c>
-      <c r="P7" s="10" t="n"/>
-      <c r="Q7" s="10" t="n"/>
-      <c r="R7" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" s="11" t="n">
+      <c r="T7" s="9" t="n"/>
+      <c r="U7" s="9" t="n"/>
+      <c r="V7" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" s="11" t="n">
         <v>202.68</v>
       </c>
-      <c r="T7" s="11" t="n">
+      <c r="X7" s="11" t="n">
         <v>2712.35</v>
       </c>
-      <c r="U7" s="11" t="n">
+      <c r="Y7" s="11" t="n">
         <v>122.06</v>
       </c>
-      <c r="V7" s="11" t="n">
+      <c r="Z7" s="11" t="n">
         <v>83</v>
       </c>
-      <c r="W7" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y7" s="11" t="n">
+      <c r="AA7" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="11" t="n">
         <v>45</v>
       </c>
-      <c r="Z7" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA7" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB7" s="11" t="n">
+      <c r="AD7" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" s="11" t="n">
         <v>2962.41</v>
       </c>
-      <c r="AC7" s="8" t="inlineStr">
+      <c r="AG7" s="8" t="inlineStr">
         <is>
           <t>Überfakturierung</t>
         </is>
@@ -1154,97 +1202,103 @@
           <t>32892399</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="8" t="n"/>
+      <c r="D8" s="8" t="n"/>
+      <c r="E8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="8" t="inlineStr"/>
+      <c r="G8" s="8" t="inlineStr">
         <is>
           <t>3767099</t>
         </is>
       </c>
-      <c r="D8" s="9" t="n">
+      <c r="H8" s="10" t="n">
         <v>45790</v>
       </c>
-      <c r="E8" s="8" t="inlineStr">
+      <c r="I8" s="8" t="inlineStr">
         <is>
           <t>Sika Supply Center GmbH</t>
         </is>
       </c>
-      <c r="F8" s="8" t="inlineStr">
+      <c r="J8" s="8" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="G8" s="8" t="inlineStr">
+      <c r="K8" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">LU5 5    </t>
         </is>
       </c>
-      <c r="H8" s="8" t="inlineStr">
+      <c r="L8" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">70499    </t>
         </is>
       </c>
-      <c r="I8" s="8" t="inlineStr">
+      <c r="M8" s="8" t="inlineStr">
         <is>
           <t>bis 2 Stpl</t>
         </is>
       </c>
-      <c r="J8" s="8" t="inlineStr">
+      <c r="N8" s="8" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="K8" s="8" t="inlineStr">
+      <c r="O8" s="8" t="inlineStr">
         <is>
           <t>EUR/Stpl</t>
         </is>
       </c>
-      <c r="L8" s="10" t="n">
+      <c r="P8" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="M8" s="11" t="n">
+      <c r="Q8" s="11" t="n">
         <v>202.68</v>
       </c>
-      <c r="N8" s="11" t="n">
+      <c r="R8" s="11" t="n">
         <v>2712.35</v>
       </c>
-      <c r="O8" s="10" t="n">
+      <c r="S8" s="9" t="n">
         <v>22675</v>
       </c>
-      <c r="P8" s="10" t="n"/>
-      <c r="Q8" s="10" t="n"/>
-      <c r="R8" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" s="11" t="n">
+      <c r="T8" s="9" t="n"/>
+      <c r="U8" s="9" t="n"/>
+      <c r="V8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" s="11" t="n">
         <v>202.68</v>
       </c>
-      <c r="T8" s="11" t="n">
+      <c r="X8" s="11" t="n">
         <v>2712.35</v>
       </c>
-      <c r="U8" s="11" t="n">
+      <c r="Y8" s="11" t="n">
         <v>122.06</v>
       </c>
-      <c r="V8" s="11" t="n">
+      <c r="Z8" s="11" t="n">
         <v>83</v>
       </c>
-      <c r="W8" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y8" s="11" t="n">
+      <c r="AA8" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="11" t="n">
         <v>45</v>
       </c>
-      <c r="Z8" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA8" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB8" s="11" t="n">
+      <c r="AD8" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" s="11" t="n">
         <v>2962.41</v>
       </c>
-      <c r="AC8" s="8" t="inlineStr">
+      <c r="AG8" s="8" t="inlineStr">
         <is>
           <t>Überfakturierung</t>
         </is>
@@ -1261,95 +1315,101 @@
           <t>32957738</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr">
+      <c r="C9" s="4" t="n"/>
+      <c r="D9" s="4" t="n"/>
+      <c r="E9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="4" t="inlineStr"/>
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>3782424</t>
         </is>
       </c>
-      <c r="D9" s="5" t="n">
+      <c r="H9" s="6" t="n">
         <v>45926</v>
       </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="I9" s="4" t="inlineStr">
         <is>
           <t>Sika Supply Center GmbH</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="J9" s="4" t="inlineStr">
         <is>
           <t>GB</t>
         </is>
       </c>
-      <c r="G9" s="4" t="inlineStr">
+      <c r="K9" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">LU5 5    </t>
         </is>
       </c>
-      <c r="H9" s="4" t="inlineStr">
+      <c r="L9" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">70499    </t>
         </is>
       </c>
-      <c r="I9" s="4" t="inlineStr">
+      <c r="M9" s="4" t="inlineStr">
         <is>
           <t>bis 2 Stpl</t>
         </is>
       </c>
-      <c r="J9" s="4" t="inlineStr">
+      <c r="N9" s="4" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="K9" s="4" t="inlineStr">
+      <c r="O9" s="4" t="inlineStr">
         <is>
           <t>EUR/Stpl</t>
         </is>
       </c>
-      <c r="L9" s="6" t="n">
+      <c r="P9" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="M9" s="7" t="n">
+      <c r="Q9" s="7" t="n">
         <v>202.68</v>
       </c>
-      <c r="N9" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" s="6" t="n">
+      <c r="R9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" s="5" t="n">
         <v>112</v>
       </c>
-      <c r="P9" s="6" t="n"/>
-      <c r="Q9" s="6" t="n">
+      <c r="T9" s="5" t="n"/>
+      <c r="U9" s="5" t="n">
         <v>0.4</v>
       </c>
-      <c r="R9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" s="7" t="n">
+      <c r="V9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" s="7" t="n">
         <v>202.68</v>
       </c>
-      <c r="T9" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W9" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" s="7" t="n"/>
+      <c r="X9" s="7" t="n">
+        <v>0</v>
+      </c>
       <c r="Y9" s="7" t="n">
         <v>0</v>
       </c>
       <c r="Z9" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="AA9" s="7" t="n"/>
-      <c r="AB9" s="7" t="n">
+      <c r="AA9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" s="7" t="n"/>
+      <c r="AC9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" s="7" t="n"/>
+      <c r="AF9" s="7" t="n">
         <v>128.11</v>
       </c>
-      <c r="AC9" s="4" t="inlineStr">
+      <c r="AG9" s="4" t="inlineStr">
         <is>
           <t>Unterfakturierung</t>
         </is>
@@ -1373,97 +1433,103 @@
           <t>32871393</t>
         </is>
       </c>
-      <c r="C12" s="4" t="inlineStr">
+      <c r="C12" s="4" t="n"/>
+      <c r="D12" s="4" t="n"/>
+      <c r="E12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="4" t="inlineStr"/>
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>3763114</t>
         </is>
       </c>
-      <c r="D12" s="5" t="n">
+      <c r="H12" s="6" t="n">
         <v>45749</v>
       </c>
-      <c r="E12" s="4" t="inlineStr">
+      <c r="I12" s="4" t="inlineStr">
         <is>
           <t>Sika Supply Center GmbH</t>
         </is>
       </c>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="J12" s="4" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="K12" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">41049    </t>
         </is>
       </c>
-      <c r="H12" s="4" t="inlineStr">
+      <c r="L12" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">70499    </t>
         </is>
       </c>
-      <c r="I12" s="4" t="inlineStr">
+      <c r="M12" s="4" t="inlineStr">
         <is>
           <t>bis 2 Stpl</t>
         </is>
       </c>
-      <c r="J12" s="4" t="inlineStr">
+      <c r="N12" s="4" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="K12" s="4" t="inlineStr">
+      <c r="O12" s="4" t="inlineStr">
         <is>
           <t>EUR/Stpl</t>
         </is>
       </c>
-      <c r="L12" s="6" t="n">
+      <c r="P12" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="M12" s="7" t="n">
+      <c r="Q12" s="7" t="n">
         <v>132.66</v>
       </c>
-      <c r="N12" s="7" t="n">
+      <c r="R12" s="7" t="n">
         <v>1154.6</v>
       </c>
-      <c r="O12" s="6" t="n">
+      <c r="S12" s="5" t="n">
         <v>20714</v>
       </c>
-      <c r="P12" s="6" t="n"/>
-      <c r="Q12" s="6" t="n"/>
-      <c r="R12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" s="7" t="n">
+      <c r="T12" s="5" t="n"/>
+      <c r="U12" s="5" t="n"/>
+      <c r="V12" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" s="7" t="n">
         <v>132.66</v>
       </c>
-      <c r="T12" s="7" t="n">
+      <c r="X12" s="7" t="n">
         <v>1154.6</v>
       </c>
-      <c r="U12" s="7" t="n">
+      <c r="Y12" s="7" t="n">
         <v>51.96</v>
       </c>
-      <c r="V12" s="7" t="n">
+      <c r="Z12" s="7" t="n">
         <v>56</v>
       </c>
-      <c r="W12" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X12" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y12" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z12" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="AA12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" s="7" t="n">
         <v>95</v>
       </c>
-      <c r="AB12" s="7" t="n">
+      <c r="AF12" s="7" t="n">
         <v>1357.56</v>
       </c>
-      <c r="AC12" s="4" t="inlineStr">
+      <c r="AG12" s="4" t="inlineStr">
         <is>
           <t>Überfakturierung</t>
         </is>
@@ -1480,97 +1546,103 @@
           <t>32871391</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="C13" s="8" t="n"/>
+      <c r="D13" s="8" t="n"/>
+      <c r="E13" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="8" t="inlineStr"/>
+      <c r="G13" s="8" t="inlineStr">
         <is>
           <t>3763114</t>
         </is>
       </c>
-      <c r="D13" s="9" t="n">
+      <c r="H13" s="10" t="n">
         <v>45749</v>
       </c>
-      <c r="E13" s="8" t="inlineStr">
+      <c r="I13" s="8" t="inlineStr">
         <is>
           <t>Sika Supply Center GmbH</t>
         </is>
       </c>
-      <c r="F13" s="8" t="inlineStr">
+      <c r="J13" s="8" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="G13" s="8" t="inlineStr">
+      <c r="K13" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">41049    </t>
         </is>
       </c>
-      <c r="H13" s="8" t="inlineStr">
+      <c r="L13" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">70499    </t>
         </is>
       </c>
-      <c r="I13" s="8" t="inlineStr">
+      <c r="M13" s="8" t="inlineStr">
         <is>
           <t>bis 2 Stpl</t>
         </is>
       </c>
-      <c r="J13" s="8" t="inlineStr">
+      <c r="N13" s="8" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="K13" s="8" t="inlineStr">
+      <c r="O13" s="8" t="inlineStr">
         <is>
           <t>EUR/Stpl</t>
         </is>
       </c>
-      <c r="L13" s="10" t="n">
+      <c r="P13" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="M13" s="11" t="n">
+      <c r="Q13" s="11" t="n">
         <v>132.66</v>
       </c>
-      <c r="N13" s="11" t="n">
+      <c r="R13" s="11" t="n">
         <v>1154.6</v>
       </c>
-      <c r="O13" s="10" t="n">
+      <c r="S13" s="9" t="n">
         <v>22570</v>
       </c>
-      <c r="P13" s="10" t="n"/>
-      <c r="Q13" s="10" t="n"/>
-      <c r="R13" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" s="11" t="n">
+      <c r="T13" s="9" t="n"/>
+      <c r="U13" s="9" t="n"/>
+      <c r="V13" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" s="11" t="n">
         <v>132.66</v>
       </c>
-      <c r="T13" s="11" t="n">
+      <c r="X13" s="11" t="n">
         <v>1154.6</v>
       </c>
-      <c r="U13" s="11" t="n">
+      <c r="Y13" s="11" t="n">
         <v>51.96</v>
       </c>
-      <c r="V13" s="11" t="n">
+      <c r="Z13" s="11" t="n">
         <v>56</v>
       </c>
-      <c r="W13" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y13" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z13" s="11" t="n">
-        <v>0</v>
-      </c>
       <c r="AA13" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" s="11" t="n">
         <v>95</v>
       </c>
-      <c r="AB13" s="11" t="n">
+      <c r="AF13" s="11" t="n">
         <v>1357.56</v>
       </c>
-      <c r="AC13" s="8" t="inlineStr">
+      <c r="AG13" s="8" t="inlineStr">
         <is>
           <t>Überfakturierung</t>
         </is>
@@ -1587,99 +1659,105 @@
           <t>32871241</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
+      <c r="C14" s="8" t="n"/>
+      <c r="D14" s="8" t="n"/>
+      <c r="E14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="8" t="inlineStr"/>
+      <c r="G14" s="8" t="inlineStr">
         <is>
           <t>3763114</t>
         </is>
       </c>
-      <c r="D14" s="9" t="n">
+      <c r="H14" s="10" t="n">
         <v>45750</v>
       </c>
-      <c r="E14" s="8" t="inlineStr">
+      <c r="I14" s="8" t="inlineStr">
         <is>
           <t>Sika Supply Center GmbH</t>
         </is>
       </c>
-      <c r="F14" s="8" t="inlineStr">
+      <c r="J14" s="8" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="G14" s="8" t="inlineStr">
+      <c r="K14" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">41049    </t>
         </is>
       </c>
-      <c r="H14" s="8" t="inlineStr">
+      <c r="L14" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">70499    </t>
         </is>
       </c>
-      <c r="I14" s="8" t="inlineStr">
+      <c r="M14" s="8" t="inlineStr">
         <is>
           <t>bis 2 Stpl</t>
         </is>
       </c>
-      <c r="J14" s="8" t="inlineStr">
+      <c r="N14" s="8" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="K14" s="8" t="inlineStr">
+      <c r="O14" s="8" t="inlineStr">
         <is>
           <t>EUR/Stpl</t>
         </is>
       </c>
-      <c r="L14" s="10" t="n">
+      <c r="P14" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="M14" s="11" t="n">
+      <c r="Q14" s="11" t="n">
         <v>110.25</v>
       </c>
-      <c r="N14" s="11" t="n">
+      <c r="R14" s="11" t="n">
         <v>23.445</v>
       </c>
-      <c r="O14" s="10" t="n">
+      <c r="S14" s="9" t="n">
         <v>484</v>
       </c>
-      <c r="P14" s="10" t="n"/>
-      <c r="Q14" s="10" t="n">
+      <c r="T14" s="9" t="n"/>
+      <c r="U14" s="9" t="n">
         <v>0.8</v>
       </c>
-      <c r="R14" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" s="11" t="n">
+      <c r="V14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" s="11" t="n">
         <v>220.5</v>
       </c>
-      <c r="T14" s="11" t="n">
+      <c r="X14" s="11" t="n">
         <v>46.89</v>
       </c>
-      <c r="U14" s="11" t="n">
+      <c r="Y14" s="11" t="n">
         <v>1.06</v>
       </c>
-      <c r="V14" s="11" t="n">
+      <c r="Z14" s="11" t="n">
         <v>0.89</v>
       </c>
-      <c r="W14" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="11" t="n">
-        <v>0</v>
-      </c>
       <c r="AA14" s="11" t="n">
         <v>0</v>
       </c>
       <c r="AB14" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="11" t="n">
         <v>48.84</v>
       </c>
-      <c r="AC14" s="8" t="inlineStr">
+      <c r="AG14" s="8" t="inlineStr">
         <is>
           <t>Unterfakturierung</t>
         </is>
@@ -1696,97 +1774,103 @@
           <t>32873796</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
+      <c r="C15" s="8" t="n"/>
+      <c r="D15" s="8" t="n"/>
+      <c r="E15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" s="8" t="inlineStr"/>
+      <c r="G15" s="8" t="inlineStr">
         <is>
           <t>3763114</t>
         </is>
       </c>
-      <c r="D15" s="9" t="n">
+      <c r="H15" s="10" t="n">
         <v>45754</v>
       </c>
-      <c r="E15" s="8" t="inlineStr">
+      <c r="I15" s="8" t="inlineStr">
         <is>
           <t>Sika Supply Center GmbH</t>
         </is>
       </c>
-      <c r="F15" s="8" t="inlineStr">
+      <c r="J15" s="8" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="G15" s="8" t="inlineStr">
+      <c r="K15" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">41049    </t>
         </is>
       </c>
-      <c r="H15" s="8" t="inlineStr">
+      <c r="L15" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">70499    </t>
         </is>
       </c>
-      <c r="I15" s="8" t="inlineStr">
+      <c r="M15" s="8" t="inlineStr">
         <is>
           <t>bis 2 Stpl</t>
         </is>
       </c>
-      <c r="J15" s="8" t="inlineStr">
+      <c r="N15" s="8" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="K15" s="8" t="inlineStr">
+      <c r="O15" s="8" t="inlineStr">
         <is>
           <t>EUR/Stpl</t>
         </is>
       </c>
-      <c r="L15" s="10" t="n">
+      <c r="P15" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="M15" s="11" t="n">
+      <c r="Q15" s="11" t="n">
         <v>132.66</v>
       </c>
-      <c r="N15" s="11" t="n">
+      <c r="R15" s="11" t="n">
         <v>1154.6</v>
       </c>
-      <c r="O15" s="10" t="n">
+      <c r="S15" s="9" t="n">
         <v>21521</v>
       </c>
-      <c r="P15" s="10" t="n"/>
-      <c r="Q15" s="10" t="n"/>
-      <c r="R15" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" s="11" t="n">
+      <c r="T15" s="9" t="n"/>
+      <c r="U15" s="9" t="n"/>
+      <c r="V15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" s="11" t="n">
         <v>132.66</v>
       </c>
-      <c r="T15" s="11" t="n">
+      <c r="X15" s="11" t="n">
         <v>1154.6</v>
       </c>
-      <c r="U15" s="11" t="n">
+      <c r="Y15" s="11" t="n">
         <v>51.96</v>
       </c>
-      <c r="V15" s="11" t="n">
+      <c r="Z15" s="11" t="n">
         <v>56</v>
       </c>
-      <c r="W15" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y15" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z15" s="11" t="n">
-        <v>0</v>
-      </c>
       <c r="AA15" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" s="11" t="n">
         <v>95</v>
       </c>
-      <c r="AB15" s="11" t="n">
+      <c r="AF15" s="11" t="n">
         <v>1357.56</v>
       </c>
-      <c r="AC15" s="8" t="inlineStr">
+      <c r="AG15" s="8" t="inlineStr">
         <is>
           <t>Überfakturierung</t>
         </is>
@@ -1803,97 +1887,103 @@
           <t>32875467</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr">
+      <c r="C16" s="8" t="n"/>
+      <c r="D16" s="8" t="n"/>
+      <c r="E16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="8" t="inlineStr"/>
+      <c r="G16" s="8" t="inlineStr">
         <is>
           <t>3763114</t>
         </is>
       </c>
-      <c r="D16" s="9" t="n">
+      <c r="H16" s="10" t="n">
         <v>45756</v>
       </c>
-      <c r="E16" s="8" t="inlineStr">
+      <c r="I16" s="8" t="inlineStr">
         <is>
           <t>Sika Supply Center GmbH</t>
         </is>
       </c>
-      <c r="F16" s="8" t="inlineStr">
+      <c r="J16" s="8" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="G16" s="8" t="inlineStr">
+      <c r="K16" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">41049    </t>
         </is>
       </c>
-      <c r="H16" s="8" t="inlineStr">
+      <c r="L16" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">70499    </t>
         </is>
       </c>
-      <c r="I16" s="8" t="inlineStr">
+      <c r="M16" s="8" t="inlineStr">
         <is>
           <t>bis 2 Stpl</t>
         </is>
       </c>
-      <c r="J16" s="8" t="inlineStr">
+      <c r="N16" s="8" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="K16" s="8" t="inlineStr">
+      <c r="O16" s="8" t="inlineStr">
         <is>
           <t>EUR/Stpl</t>
         </is>
       </c>
-      <c r="L16" s="10" t="n">
+      <c r="P16" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="M16" s="11" t="n">
+      <c r="Q16" s="11" t="n">
         <v>132.66</v>
       </c>
-      <c r="N16" s="11" t="n">
+      <c r="R16" s="11" t="n">
         <v>1154.6</v>
       </c>
-      <c r="O16" s="10" t="n">
+      <c r="S16" s="9" t="n">
         <v>21190</v>
       </c>
-      <c r="P16" s="10" t="n"/>
-      <c r="Q16" s="10" t="n"/>
-      <c r="R16" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" s="11" t="n">
+      <c r="T16" s="9" t="n"/>
+      <c r="U16" s="9" t="n"/>
+      <c r="V16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" s="11" t="n">
         <v>132.66</v>
       </c>
-      <c r="T16" s="11" t="n">
+      <c r="X16" s="11" t="n">
         <v>1154.6</v>
       </c>
-      <c r="U16" s="11" t="n">
+      <c r="Y16" s="11" t="n">
         <v>51.96</v>
       </c>
-      <c r="V16" s="11" t="n">
+      <c r="Z16" s="11" t="n">
         <v>56</v>
       </c>
-      <c r="W16" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X16" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y16" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z16" s="11" t="n">
-        <v>0</v>
-      </c>
       <c r="AA16" s="11" t="n">
         <v>0</v>
       </c>
       <c r="AB16" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" s="11" t="n">
         <v>1262.56</v>
       </c>
-      <c r="AC16" s="8" t="inlineStr">
+      <c r="AG16" s="8" t="inlineStr">
         <is>
           <t>Überfakturierung</t>
         </is>
@@ -1910,101 +2000,107 @@
           <t>7092010039263000</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C17" s="4" t="n"/>
+      <c r="D17" s="4" t="n"/>
+      <c r="E17" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="4" t="inlineStr"/>
+      <c r="G17" s="4" t="inlineStr">
         <is>
           <t>4251023585</t>
         </is>
       </c>
-      <c r="D17" s="5" t="n">
+      <c r="H17" s="6" t="n">
         <v>46078</v>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="I17" s="4" t="inlineStr">
         <is>
           <t>Sika Supply Center GmbH</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="J17" s="4" t="inlineStr">
         <is>
           <t>IT</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="K17" s="4" t="inlineStr">
         <is>
           <t>41049</t>
         </is>
       </c>
-      <c r="H17" s="4" t="inlineStr">
+      <c r="L17" s="4" t="inlineStr">
         <is>
           <t>70499</t>
         </is>
       </c>
-      <c r="I17" s="4" t="inlineStr">
+      <c r="M17" s="4" t="inlineStr">
         <is>
           <t>bis 2 Stpl</t>
         </is>
       </c>
-      <c r="J17" s="4" t="inlineStr">
+      <c r="N17" s="4" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="K17" s="4" t="inlineStr">
+      <c r="O17" s="4" t="inlineStr">
         <is>
           <t>EUR/Stpl</t>
         </is>
       </c>
-      <c r="L17" s="6" t="n">
+      <c r="P17" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="M17" s="7" t="n">
+      <c r="Q17" s="7" t="n">
         <v>132.66</v>
       </c>
-      <c r="N17" s="7" t="n">
+      <c r="R17" s="7" t="n">
         <v>132.66</v>
       </c>
-      <c r="O17" s="6" t="n">
+      <c r="S17" s="5" t="n">
         <v>110</v>
       </c>
-      <c r="P17" s="6" t="n">
+      <c r="T17" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="Q17" s="6" t="n">
+      <c r="U17" s="5" t="n">
         <v>0.4</v>
       </c>
-      <c r="R17" s="6" t="n">
+      <c r="V17" s="5" t="n">
         <v>0.38</v>
       </c>
-      <c r="S17" s="7" t="n">
+      <c r="W17" s="7" t="n">
         <v>132.66</v>
       </c>
-      <c r="T17" s="7" t="n">
+      <c r="X17" s="7" t="n">
         <v>132.66</v>
       </c>
-      <c r="U17" s="7" t="n">
+      <c r="Y17" s="7" t="n">
         <v>2.48</v>
       </c>
-      <c r="V17" s="7" t="n">
+      <c r="Z17" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="W17" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y17" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z17" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="AA17" s="7" t="n">
         <v>0</v>
       </c>
       <c r="AB17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" s="7" t="n">
         <v>137.14</v>
       </c>
-      <c r="AC17" s="4" t="inlineStr">
+      <c r="AG17" s="4" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -2028,82 +2124,76 @@
           <t>32921857</t>
         </is>
       </c>
-      <c r="C20" s="4" t="inlineStr">
+      <c r="C20" s="4" t="n"/>
+      <c r="D20" s="4" t="n"/>
+      <c r="E20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="4" t="inlineStr"/>
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>3775373</t>
         </is>
       </c>
-      <c r="D20" s="5" t="n">
+      <c r="H20" s="6" t="n">
         <v>45845</v>
       </c>
-      <c r="E20" s="4" t="inlineStr">
+      <c r="I20" s="4" t="inlineStr">
         <is>
           <t>Sika Supply Center GmbH</t>
         </is>
       </c>
-      <c r="F20" s="4" t="inlineStr">
+      <c r="J20" s="4" t="inlineStr">
         <is>
           <t>PT</t>
         </is>
       </c>
-      <c r="G20" s="4" t="inlineStr">
+      <c r="K20" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">5400     </t>
         </is>
       </c>
-      <c r="H20" s="4" t="inlineStr">
+      <c r="L20" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">70499    </t>
         </is>
       </c>
-      <c r="I20" s="4" t="inlineStr">
+      <c r="M20" s="4" t="inlineStr">
         <is>
           <t>bis 33 Stpl</t>
         </is>
       </c>
-      <c r="J20" s="4" t="inlineStr">
+      <c r="N20" s="4" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="K20" s="4" t="inlineStr">
+      <c r="O20" s="4" t="inlineStr">
         <is>
           <t>EUR/Stpl</t>
         </is>
       </c>
-      <c r="L20" s="6" t="n">
+      <c r="P20" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="M20" s="7" t="n"/>
-      <c r="N20" s="7" t="n">
+      <c r="Q20" s="7" t="n"/>
+      <c r="R20" s="7" t="n">
         <v>108.3333333333333</v>
       </c>
-      <c r="O20" s="6" t="n">
+      <c r="S20" s="5" t="n">
         <v>14088</v>
       </c>
-      <c r="P20" s="6" t="n"/>
-      <c r="Q20" s="6" t="n">
+      <c r="T20" s="5" t="n"/>
+      <c r="U20" s="5" t="n">
         <v>9.6</v>
       </c>
-      <c r="R20" s="6" t="n">
+      <c r="V20" s="5" t="n">
         <v>23.04</v>
       </c>
-      <c r="S20" s="7" t="n"/>
-      <c r="T20" s="7" t="n">
+      <c r="W20" s="7" t="n"/>
+      <c r="X20" s="7" t="n">
         <v>2600</v>
       </c>
-      <c r="U20" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W20" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="Y20" s="7" t="n">
         <v>0</v>
       </c>
@@ -2114,9 +2204,21 @@
         <v>0</v>
       </c>
       <c r="AB20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" s="7" t="n">
         <v>2600</v>
       </c>
-      <c r="AC20" s="4" t="inlineStr">
+      <c r="AG20" s="4" t="inlineStr">
         <is>
           <t>Soll n/a</t>
         </is>
@@ -2133,84 +2235,78 @@
           <t>7092010014395009</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
+      <c r="C21" s="4" t="n"/>
+      <c r="D21" s="4" t="n"/>
+      <c r="E21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="4" t="inlineStr"/>
+      <c r="G21" s="4" t="inlineStr">
         <is>
           <t>4251016084</t>
         </is>
       </c>
-      <c r="D21" s="5" t="n">
+      <c r="H21" s="6" t="n">
         <v>45964</v>
       </c>
-      <c r="E21" s="4" t="inlineStr">
+      <c r="I21" s="4" t="inlineStr">
         <is>
           <t>Sika Supply Center GmbH</t>
         </is>
       </c>
-      <c r="F21" s="4" t="inlineStr">
+      <c r="J21" s="4" t="inlineStr">
         <is>
           <t>PT</t>
         </is>
       </c>
-      <c r="G21" s="4" t="inlineStr">
+      <c r="K21" s="4" t="inlineStr">
         <is>
           <t>5400</t>
         </is>
       </c>
-      <c r="H21" s="4" t="inlineStr">
+      <c r="L21" s="4" t="inlineStr">
         <is>
           <t>70499</t>
         </is>
       </c>
-      <c r="I21" s="4" t="inlineStr">
+      <c r="M21" s="4" t="inlineStr">
         <is>
           <t>bis 33 Stpl</t>
         </is>
       </c>
-      <c r="J21" s="4" t="inlineStr">
+      <c r="N21" s="4" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="K21" s="4" t="inlineStr">
+      <c r="O21" s="4" t="inlineStr">
         <is>
           <t>EUR/Stpl</t>
         </is>
       </c>
-      <c r="L21" s="6" t="n">
+      <c r="P21" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="M21" s="7" t="n"/>
-      <c r="N21" s="7" t="n">
+      <c r="Q21" s="7" t="n"/>
+      <c r="R21" s="7" t="n">
         <v>84.3850875</v>
       </c>
-      <c r="O21" s="6" t="n">
+      <c r="S21" s="5" t="n">
         <v>14088</v>
       </c>
-      <c r="P21" s="6" t="n">
+      <c r="T21" s="5" t="n">
         <v>24</v>
       </c>
-      <c r="Q21" s="6" t="n">
+      <c r="U21" s="5" t="n">
         <v>9.6</v>
       </c>
-      <c r="R21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" s="7" t="n"/>
-      <c r="T21" s="7" t="n">
+      <c r="V21" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" s="7" t="n"/>
+      <c r="X21" s="7" t="n">
         <v>2025.2421</v>
       </c>
-      <c r="U21" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W21" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X21" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="Y21" s="7" t="n">
         <v>0</v>
       </c>
@@ -2221,9 +2317,21 @@
         <v>0</v>
       </c>
       <c r="AB21" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF21" s="7" t="n">
         <v>2025.2421</v>
       </c>
-      <c r="AC21" s="4" t="inlineStr">
+      <c r="AG21" s="4" t="inlineStr">
         <is>
           <t>Soll n/a</t>
         </is>
@@ -2247,82 +2355,76 @@
           <t>32880329</t>
         </is>
       </c>
-      <c r="C24" s="8" t="inlineStr">
+      <c r="C24" s="8" t="n"/>
+      <c r="D24" s="8" t="n"/>
+      <c r="E24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="8" t="inlineStr"/>
+      <c r="G24" s="8" t="inlineStr">
         <is>
           <t>3763462</t>
         </is>
       </c>
-      <c r="D24" s="9" t="n">
+      <c r="H24" s="10" t="n">
         <v>45764</v>
       </c>
-      <c r="E24" s="8" t="inlineStr">
+      <c r="I24" s="8" t="inlineStr">
         <is>
           <t>Sika Supply Center GmbH</t>
         </is>
       </c>
-      <c r="F24" s="8" t="inlineStr">
+      <c r="J24" s="8" t="inlineStr">
         <is>
           <t>PT</t>
         </is>
       </c>
-      <c r="G24" s="8" t="inlineStr">
+      <c r="K24" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">5400     </t>
         </is>
       </c>
-      <c r="H24" s="8" t="inlineStr">
+      <c r="L24" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">70499    </t>
         </is>
       </c>
-      <c r="I24" s="8" t="inlineStr">
+      <c r="M24" s="8" t="inlineStr">
         <is>
           <t>bis 5 Stpl</t>
         </is>
       </c>
-      <c r="J24" s="8" t="inlineStr">
+      <c r="N24" s="8" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="K24" s="8" t="inlineStr">
+      <c r="O24" s="8" t="inlineStr">
         <is>
           <t>EUR/Stpl</t>
         </is>
       </c>
-      <c r="L24" s="10" t="n">
+      <c r="P24" s="9" t="n">
         <v>4</v>
       </c>
-      <c r="M24" s="11" t="n"/>
-      <c r="N24" s="11" t="n">
+      <c r="Q24" s="11" t="n"/>
+      <c r="R24" s="11" t="n">
         <v>168.75</v>
       </c>
-      <c r="O24" s="10" t="n">
+      <c r="S24" s="9" t="n">
         <v>1188</v>
       </c>
-      <c r="P24" s="10" t="n"/>
-      <c r="Q24" s="10" t="n">
+      <c r="T24" s="9" t="n"/>
+      <c r="U24" s="9" t="n">
         <v>1.6</v>
       </c>
-      <c r="R24" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" s="11" t="n"/>
-      <c r="T24" s="11" t="n">
+      <c r="V24" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" s="11" t="n"/>
+      <c r="X24" s="11" t="n">
         <v>675</v>
       </c>
-      <c r="U24" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="W24" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X24" s="11" t="n">
-        <v>0</v>
-      </c>
       <c r="Y24" s="11" t="n">
         <v>0</v>
       </c>
@@ -2333,9 +2435,21 @@
         <v>0</v>
       </c>
       <c r="AB24" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC24" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD24" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE24" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF24" s="11" t="n">
         <v>675</v>
       </c>
-      <c r="AC24" s="8" t="inlineStr">
+      <c r="AG24" s="8" t="inlineStr">
         <is>
           <t>Soll n/a</t>
         </is>
@@ -2352,82 +2466,76 @@
           <t>32921854</t>
         </is>
       </c>
-      <c r="C25" s="4" t="inlineStr">
+      <c r="C25" s="4" t="n"/>
+      <c r="D25" s="4" t="n"/>
+      <c r="E25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="4" t="inlineStr"/>
+      <c r="G25" s="4" t="inlineStr">
         <is>
           <t>3775373</t>
         </is>
       </c>
-      <c r="D25" s="5" t="n">
+      <c r="H25" s="6" t="n">
         <v>45845</v>
       </c>
-      <c r="E25" s="4" t="inlineStr">
+      <c r="I25" s="4" t="inlineStr">
         <is>
           <t>Sika Supply Center GmbH</t>
         </is>
       </c>
-      <c r="F25" s="4" t="inlineStr">
+      <c r="J25" s="4" t="inlineStr">
         <is>
           <t>PT</t>
         </is>
       </c>
-      <c r="G25" s="4" t="inlineStr">
+      <c r="K25" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">5400     </t>
         </is>
       </c>
-      <c r="H25" s="4" t="inlineStr">
+      <c r="L25" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">70499    </t>
         </is>
       </c>
-      <c r="I25" s="4" t="inlineStr">
+      <c r="M25" s="4" t="inlineStr">
         <is>
           <t>bis 5 Stpl</t>
         </is>
       </c>
-      <c r="J25" s="4" t="inlineStr">
+      <c r="N25" s="4" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="K25" s="4" t="inlineStr">
+      <c r="O25" s="4" t="inlineStr">
         <is>
           <t>EUR/Stpl</t>
         </is>
       </c>
-      <c r="L25" s="6" t="n">
+      <c r="P25" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="M25" s="7" t="n"/>
-      <c r="N25" s="7" t="n">
+      <c r="Q25" s="7" t="n"/>
+      <c r="R25" s="7" t="n">
         <v>168.75</v>
       </c>
-      <c r="O25" s="6" t="n">
+      <c r="S25" s="5" t="n">
         <v>1122</v>
       </c>
-      <c r="P25" s="6" t="n"/>
-      <c r="Q25" s="6" t="n">
+      <c r="T25" s="5" t="n"/>
+      <c r="U25" s="5" t="n">
         <v>1.2</v>
       </c>
-      <c r="R25" s="6" t="n">
+      <c r="V25" s="5" t="n">
         <v>2.88</v>
       </c>
-      <c r="S25" s="7" t="n"/>
-      <c r="T25" s="7" t="n">
+      <c r="W25" s="7" t="n"/>
+      <c r="X25" s="7" t="n">
         <v>506.25</v>
       </c>
-      <c r="U25" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W25" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X25" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="Y25" s="7" t="n">
         <v>0</v>
       </c>
@@ -2438,9 +2546,21 @@
         <v>0</v>
       </c>
       <c r="AB25" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC25" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD25" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE25" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF25" s="7" t="n">
         <v>506.25</v>
       </c>
-      <c r="AC25" s="4" t="inlineStr">
+      <c r="AG25" s="4" t="inlineStr">
         <is>
           <t>Soll n/a</t>
         </is>
@@ -2457,84 +2577,78 @@
           <t>7092010014397003</t>
         </is>
       </c>
-      <c r="C26" s="4" t="inlineStr">
+      <c r="C26" s="4" t="n"/>
+      <c r="D26" s="4" t="n"/>
+      <c r="E26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="4" t="inlineStr"/>
+      <c r="G26" s="4" t="inlineStr">
         <is>
           <t>4251016084</t>
         </is>
       </c>
-      <c r="D26" s="5" t="n">
+      <c r="H26" s="6" t="n">
         <v>45964</v>
       </c>
-      <c r="E26" s="4" t="inlineStr">
+      <c r="I26" s="4" t="inlineStr">
         <is>
           <t>Sika Supply Center GmbH</t>
         </is>
       </c>
-      <c r="F26" s="4" t="inlineStr">
+      <c r="J26" s="4" t="inlineStr">
         <is>
           <t>PT</t>
         </is>
       </c>
-      <c r="G26" s="4" t="inlineStr">
+      <c r="K26" s="4" t="inlineStr">
         <is>
           <t>5400</t>
         </is>
       </c>
-      <c r="H26" s="4" t="inlineStr">
+      <c r="L26" s="4" t="inlineStr">
         <is>
           <t>70499</t>
         </is>
       </c>
-      <c r="I26" s="4" t="inlineStr">
+      <c r="M26" s="4" t="inlineStr">
         <is>
           <t>bis 5 Stpl</t>
         </is>
       </c>
-      <c r="J26" s="4" t="inlineStr">
+      <c r="N26" s="4" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="K26" s="4" t="inlineStr">
+      <c r="O26" s="4" t="inlineStr">
         <is>
           <t>EUR/Stpl</t>
         </is>
       </c>
-      <c r="L26" s="6" t="n">
+      <c r="P26" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="M26" s="7" t="n"/>
-      <c r="N26" s="7" t="n">
+      <c r="Q26" s="7" t="n"/>
+      <c r="R26" s="7" t="n">
         <v>50.60263333333333</v>
       </c>
-      <c r="O26" s="6" t="n">
+      <c r="S26" s="5" t="n">
         <v>1056</v>
       </c>
-      <c r="P26" s="6" t="n">
+      <c r="T26" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="Q26" s="6" t="n">
+      <c r="U26" s="5" t="n">
         <v>1.2</v>
       </c>
-      <c r="R26" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" s="7" t="n"/>
-      <c r="T26" s="7" t="n">
+      <c r="V26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" s="7" t="n"/>
+      <c r="X26" s="7" t="n">
         <v>151.8079</v>
       </c>
-      <c r="U26" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W26" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X26" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="Y26" s="7" t="n">
         <v>0</v>
       </c>
@@ -2545,9 +2659,21 @@
         <v>0</v>
       </c>
       <c r="AB26" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC26" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD26" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE26" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF26" s="7" t="n">
         <v>151.8079</v>
       </c>
-      <c r="AC26" s="4" t="inlineStr">
+      <c r="AG26" s="4" t="inlineStr">
         <is>
           <t>Soll n/a</t>
         </is>
@@ -2571,95 +2697,101 @@
           <t>32880620</t>
         </is>
       </c>
-      <c r="C29" s="4" t="inlineStr">
+      <c r="C29" s="4" t="n"/>
+      <c r="D29" s="4" t="n"/>
+      <c r="E29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="4" t="inlineStr"/>
+      <c r="G29" s="4" t="inlineStr">
         <is>
           <t>3763118</t>
         </is>
       </c>
-      <c r="D29" s="5" t="n">
+      <c r="H29" s="6" t="n">
         <v>45764</v>
       </c>
-      <c r="E29" s="4" t="inlineStr">
+      <c r="I29" s="4" t="inlineStr">
         <is>
           <t>Sika Supply Center GmbH</t>
         </is>
       </c>
-      <c r="F29" s="4" t="inlineStr">
+      <c r="J29" s="4" t="inlineStr">
         <is>
           <t>IE</t>
         </is>
       </c>
-      <c r="G29" s="4" t="inlineStr">
+      <c r="K29" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">DUB      </t>
         </is>
       </c>
-      <c r="H29" s="4" t="inlineStr">
+      <c r="L29" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">70499    </t>
         </is>
       </c>
-      <c r="I29" s="4" t="inlineStr">
+      <c r="M29" s="4" t="inlineStr">
         <is>
           <t>bis 2 Stpl</t>
         </is>
       </c>
-      <c r="J29" s="4" t="inlineStr">
+      <c r="N29" s="4" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="K29" s="4" t="inlineStr">
+      <c r="O29" s="4" t="inlineStr">
         <is>
           <t>EUR/Stpl</t>
         </is>
       </c>
-      <c r="L29" s="6" t="n">
+      <c r="P29" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="M29" s="7" t="n"/>
-      <c r="N29" s="7" t="n">
+      <c r="Q29" s="7" t="n"/>
+      <c r="R29" s="7" t="n">
         <v>121.53</v>
       </c>
-      <c r="O29" s="6" t="n">
+      <c r="S29" s="5" t="n">
         <v>669</v>
       </c>
-      <c r="P29" s="6" t="n"/>
-      <c r="Q29" s="6" t="n">
+      <c r="T29" s="5" t="n"/>
+      <c r="U29" s="5" t="n">
         <v>0.4</v>
       </c>
-      <c r="R29" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" s="7" t="n"/>
-      <c r="T29" s="7" t="n">
+      <c r="V29" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" s="7" t="n"/>
+      <c r="X29" s="7" t="n">
         <v>121.53</v>
       </c>
-      <c r="U29" s="7" t="n">
+      <c r="Y29" s="7" t="n">
         <v>2.73</v>
       </c>
-      <c r="V29" s="7" t="n">
+      <c r="Z29" s="7" t="n">
         <v>2.48</v>
       </c>
-      <c r="W29" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X29" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y29" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z29" s="7" t="n">
-        <v>0</v>
-      </c>
       <c r="AA29" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD29" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE29" s="7" t="n">
         <v>1.82</v>
       </c>
-      <c r="AB29" s="7" t="n">
+      <c r="AF29" s="7" t="n">
         <v>128.56</v>
       </c>
-      <c r="AC29" s="4" t="inlineStr">
+      <c r="AG29" s="4" t="inlineStr">
         <is>
           <t>Soll n/a</t>
         </is>
@@ -2676,93 +2808,99 @@
           <t>32883325</t>
         </is>
       </c>
-      <c r="C30" s="8" t="inlineStr">
+      <c r="C30" s="8" t="n"/>
+      <c r="D30" s="8" t="n"/>
+      <c r="E30" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" s="8" t="inlineStr"/>
+      <c r="G30" s="8" t="inlineStr">
         <is>
           <t>3763118</t>
         </is>
       </c>
-      <c r="D30" s="9" t="n">
+      <c r="H30" s="10" t="n">
         <v>45772</v>
       </c>
-      <c r="E30" s="8" t="inlineStr">
+      <c r="I30" s="8" t="inlineStr">
         <is>
           <t>Sika Supply Center GmbH</t>
         </is>
       </c>
-      <c r="F30" s="8" t="inlineStr">
+      <c r="J30" s="8" t="inlineStr">
         <is>
           <t>IE</t>
         </is>
       </c>
-      <c r="G30" s="8" t="inlineStr">
+      <c r="K30" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">DUB      </t>
         </is>
       </c>
-      <c r="H30" s="8" t="inlineStr">
+      <c r="L30" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">70499    </t>
         </is>
       </c>
-      <c r="I30" s="8" t="inlineStr">
+      <c r="M30" s="8" t="inlineStr">
         <is>
           <t>bis 2 Stpl</t>
         </is>
       </c>
-      <c r="J30" s="8" t="inlineStr">
+      <c r="N30" s="8" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="K30" s="8" t="inlineStr">
+      <c r="O30" s="8" t="inlineStr">
         <is>
           <t>EUR/Stpl</t>
         </is>
       </c>
-      <c r="L30" s="10" t="n">
+      <c r="P30" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="M30" s="11" t="n"/>
-      <c r="N30" s="11" t="n">
+      <c r="Q30" s="11" t="n"/>
+      <c r="R30" s="11" t="n">
         <v>3706.45</v>
       </c>
-      <c r="O30" s="10" t="n">
+      <c r="S30" s="9" t="n">
         <v>22681</v>
       </c>
-      <c r="P30" s="10" t="n"/>
-      <c r="Q30" s="10" t="n"/>
-      <c r="R30" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" s="11" t="n"/>
-      <c r="T30" s="11" t="n">
+      <c r="T30" s="9" t="n"/>
+      <c r="U30" s="9" t="n"/>
+      <c r="V30" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" s="11" t="n"/>
+      <c r="X30" s="11" t="n">
         <v>3706.45</v>
       </c>
-      <c r="U30" s="11" t="n">
+      <c r="Y30" s="11" t="n">
         <v>166.79</v>
       </c>
-      <c r="V30" s="11" t="n">
+      <c r="Z30" s="11" t="n">
         <v>68</v>
       </c>
-      <c r="W30" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X30" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y30" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z30" s="11" t="n">
-        <v>0</v>
-      </c>
       <c r="AA30" s="11" t="n">
         <v>0</v>
       </c>
       <c r="AB30" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC30" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE30" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF30" s="11" t="n">
         <v>3941.24</v>
       </c>
-      <c r="AC30" s="8" t="inlineStr">
+      <c r="AG30" s="8" t="inlineStr">
         <is>
           <t>Soll n/a</t>
         </is>
@@ -2779,95 +2917,101 @@
           <t>32902680</t>
         </is>
       </c>
-      <c r="C31" s="8" t="inlineStr">
+      <c r="C31" s="8" t="n"/>
+      <c r="D31" s="8" t="n"/>
+      <c r="E31" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="8" t="inlineStr"/>
+      <c r="G31" s="8" t="inlineStr">
         <is>
           <t>3767100</t>
         </is>
       </c>
-      <c r="D31" s="9" t="n">
+      <c r="H31" s="10" t="n">
         <v>45807</v>
       </c>
-      <c r="E31" s="8" t="inlineStr">
+      <c r="I31" s="8" t="inlineStr">
         <is>
           <t>Sika Supply Center GmbH</t>
         </is>
       </c>
-      <c r="F31" s="8" t="inlineStr">
+      <c r="J31" s="8" t="inlineStr">
         <is>
           <t>IE</t>
         </is>
       </c>
-      <c r="G31" s="8" t="inlineStr">
+      <c r="K31" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">DUB      </t>
         </is>
       </c>
-      <c r="H31" s="8" t="inlineStr">
+      <c r="L31" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">70499    </t>
         </is>
       </c>
-      <c r="I31" s="8" t="inlineStr">
+      <c r="M31" s="8" t="inlineStr">
         <is>
           <t>bis 2 Stpl</t>
         </is>
       </c>
-      <c r="J31" s="8" t="inlineStr">
+      <c r="N31" s="8" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="K31" s="8" t="inlineStr">
+      <c r="O31" s="8" t="inlineStr">
         <is>
           <t>EUR/Stpl</t>
         </is>
       </c>
-      <c r="L31" s="10" t="n">
+      <c r="P31" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="M31" s="11" t="n"/>
-      <c r="N31" s="11" t="n">
+      <c r="Q31" s="11" t="n"/>
+      <c r="R31" s="11" t="n">
         <v>127.07</v>
       </c>
-      <c r="O31" s="10" t="n">
+      <c r="S31" s="9" t="n">
         <v>472</v>
       </c>
-      <c r="P31" s="10" t="n"/>
-      <c r="Q31" s="10" t="n">
+      <c r="T31" s="9" t="n"/>
+      <c r="U31" s="9" t="n">
         <v>0.4</v>
       </c>
-      <c r="R31" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" s="11" t="n"/>
-      <c r="T31" s="11" t="n">
+      <c r="V31" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" s="11" t="n"/>
+      <c r="X31" s="11" t="n">
         <v>127.07</v>
       </c>
-      <c r="U31" s="11" t="n">
+      <c r="Y31" s="11" t="n">
         <v>2.86</v>
       </c>
-      <c r="V31" s="11" t="n">
+      <c r="Z31" s="11" t="n">
         <v>2.4</v>
       </c>
-      <c r="W31" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X31" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y31" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z31" s="11" t="n">
-        <v>0</v>
-      </c>
       <c r="AA31" s="11" t="n">
         <v>0</v>
       </c>
       <c r="AB31" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC31" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD31" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE31" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF31" s="11" t="n">
         <v>132.33</v>
       </c>
-      <c r="AC31" s="8" t="inlineStr">
+      <c r="AG31" s="8" t="inlineStr">
         <is>
           <t>Soll n/a</t>
         </is>
@@ -2884,93 +3028,99 @@
           <t>32917068</t>
         </is>
       </c>
-      <c r="C32" s="8" t="inlineStr">
+      <c r="C32" s="8" t="n"/>
+      <c r="D32" s="8" t="n"/>
+      <c r="E32" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="8" t="inlineStr"/>
+      <c r="G32" s="8" t="inlineStr">
         <is>
           <t>3771128</t>
         </is>
       </c>
-      <c r="D32" s="9" t="n">
+      <c r="H32" s="10" t="n">
         <v>45835</v>
       </c>
-      <c r="E32" s="8" t="inlineStr">
+      <c r="I32" s="8" t="inlineStr">
         <is>
           <t>Sika Supply Center GmbH</t>
         </is>
       </c>
-      <c r="F32" s="8" t="inlineStr">
+      <c r="J32" s="8" t="inlineStr">
         <is>
           <t>IE</t>
         </is>
       </c>
-      <c r="G32" s="8" t="inlineStr">
+      <c r="K32" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">DUB      </t>
         </is>
       </c>
-      <c r="H32" s="8" t="inlineStr">
+      <c r="L32" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">70499    </t>
         </is>
       </c>
-      <c r="I32" s="8" t="inlineStr">
+      <c r="M32" s="8" t="inlineStr">
         <is>
           <t>bis 2 Stpl</t>
         </is>
       </c>
-      <c r="J32" s="8" t="inlineStr">
+      <c r="N32" s="8" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="K32" s="8" t="inlineStr">
+      <c r="O32" s="8" t="inlineStr">
         <is>
           <t>EUR/Stpl</t>
         </is>
       </c>
-      <c r="L32" s="10" t="n">
+      <c r="P32" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="M32" s="11" t="n"/>
-      <c r="N32" s="11" t="n">
+      <c r="Q32" s="11" t="n"/>
+      <c r="R32" s="11" t="n">
         <v>3706.45</v>
       </c>
-      <c r="O32" s="10" t="n">
+      <c r="S32" s="9" t="n">
         <v>19971</v>
       </c>
-      <c r="P32" s="10" t="n"/>
-      <c r="Q32" s="10" t="n"/>
-      <c r="R32" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" s="11" t="n"/>
-      <c r="T32" s="11" t="n">
+      <c r="T32" s="9" t="n"/>
+      <c r="U32" s="9" t="n"/>
+      <c r="V32" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" s="11" t="n"/>
+      <c r="X32" s="11" t="n">
         <v>3706.45</v>
       </c>
-      <c r="U32" s="11" t="n">
+      <c r="Y32" s="11" t="n">
         <v>166.79</v>
       </c>
-      <c r="V32" s="11" t="n">
+      <c r="Z32" s="11" t="n">
         <v>68</v>
       </c>
-      <c r="W32" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X32" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y32" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z32" s="11" t="n">
-        <v>0</v>
-      </c>
       <c r="AA32" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB32" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC32" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD32" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE32" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="AB32" s="11" t="n">
+      <c r="AF32" s="11" t="n">
         <v>3971.24</v>
       </c>
-      <c r="AC32" s="8" t="inlineStr">
+      <c r="AG32" s="8" t="inlineStr">
         <is>
           <t>Soll n/a</t>
         </is>
@@ -2987,93 +3137,99 @@
           <t>32921289</t>
         </is>
       </c>
-      <c r="C33" s="8" t="inlineStr">
+      <c r="C33" s="8" t="n"/>
+      <c r="D33" s="8" t="n"/>
+      <c r="E33" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="8" t="inlineStr"/>
+      <c r="G33" s="8" t="inlineStr">
         <is>
           <t>3775375</t>
         </is>
       </c>
-      <c r="D33" s="9" t="n">
+      <c r="H33" s="10" t="n">
         <v>45842</v>
       </c>
-      <c r="E33" s="8" t="inlineStr">
+      <c r="I33" s="8" t="inlineStr">
         <is>
           <t>Sika Supply Center GmbH</t>
         </is>
       </c>
-      <c r="F33" s="8" t="inlineStr">
+      <c r="J33" s="8" t="inlineStr">
         <is>
           <t>IE</t>
         </is>
       </c>
-      <c r="G33" s="8" t="inlineStr">
+      <c r="K33" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">DUB      </t>
         </is>
       </c>
-      <c r="H33" s="8" t="inlineStr">
+      <c r="L33" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">70499    </t>
         </is>
       </c>
-      <c r="I33" s="8" t="inlineStr">
+      <c r="M33" s="8" t="inlineStr">
         <is>
           <t>bis 2 Stpl</t>
         </is>
       </c>
-      <c r="J33" s="8" t="inlineStr">
+      <c r="N33" s="8" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="K33" s="8" t="inlineStr">
+      <c r="O33" s="8" t="inlineStr">
         <is>
           <t>EUR/Stpl</t>
         </is>
       </c>
-      <c r="L33" s="10" t="n">
+      <c r="P33" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="M33" s="11" t="n"/>
-      <c r="N33" s="11" t="n">
+      <c r="Q33" s="11" t="n"/>
+      <c r="R33" s="11" t="n">
         <v>3706.45</v>
       </c>
-      <c r="O33" s="10" t="n">
+      <c r="S33" s="9" t="n">
         <v>13493</v>
       </c>
-      <c r="P33" s="10" t="n"/>
-      <c r="Q33" s="10" t="n"/>
-      <c r="R33" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" s="11" t="n"/>
-      <c r="T33" s="11" t="n">
+      <c r="T33" s="9" t="n"/>
+      <c r="U33" s="9" t="n"/>
+      <c r="V33" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" s="11" t="n"/>
+      <c r="X33" s="11" t="n">
         <v>3706.45</v>
       </c>
-      <c r="U33" s="11" t="n">
+      <c r="Y33" s="11" t="n">
         <v>131.21</v>
       </c>
-      <c r="V33" s="11" t="n">
+      <c r="Z33" s="11" t="n">
         <v>68</v>
       </c>
-      <c r="W33" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X33" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y33" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z33" s="11" t="n">
-        <v>0</v>
-      </c>
       <c r="AA33" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB33" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC33" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD33" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE33" s="11" t="n">
         <v>30</v>
       </c>
-      <c r="AB33" s="11" t="n">
+      <c r="AF33" s="11" t="n">
         <v>3935.66</v>
       </c>
-      <c r="AC33" s="8" t="inlineStr">
+      <c r="AG33" s="8" t="inlineStr">
         <is>
           <t>Soll n/a</t>
         </is>
@@ -3090,91 +3246,97 @@
           <t>32957832</t>
         </is>
       </c>
-      <c r="C34" s="4" t="inlineStr">
+      <c r="C34" s="4" t="n"/>
+      <c r="D34" s="4" t="n"/>
+      <c r="E34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="4" t="inlineStr"/>
+      <c r="G34" s="4" t="inlineStr">
         <is>
           <t>3782425</t>
         </is>
       </c>
-      <c r="D34" s="5" t="n">
+      <c r="H34" s="6" t="n">
         <v>45926</v>
       </c>
-      <c r="E34" s="4" t="inlineStr">
+      <c r="I34" s="4" t="inlineStr">
         <is>
           <t>Sika Supply Center GmbH</t>
         </is>
       </c>
-      <c r="F34" s="4" t="inlineStr">
+      <c r="J34" s="4" t="inlineStr">
         <is>
           <t>IE</t>
         </is>
       </c>
-      <c r="G34" s="4" t="inlineStr">
+      <c r="K34" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">DUB      </t>
         </is>
       </c>
-      <c r="H34" s="4" t="inlineStr">
+      <c r="L34" s="4" t="inlineStr">
         <is>
           <t xml:space="preserve">70499    </t>
         </is>
       </c>
-      <c r="I34" s="4" t="inlineStr">
+      <c r="M34" s="4" t="inlineStr">
         <is>
           <t>bis 2 Stpl</t>
         </is>
       </c>
-      <c r="J34" s="4" t="inlineStr">
+      <c r="N34" s="4" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="K34" s="4" t="inlineStr">
+      <c r="O34" s="4" t="inlineStr">
         <is>
           <t>EUR/Stpl</t>
         </is>
       </c>
-      <c r="L34" s="6" t="n">
+      <c r="P34" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="M34" s="7" t="n"/>
-      <c r="N34" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" s="6" t="n">
+      <c r="Q34" s="7" t="n"/>
+      <c r="R34" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" s="5" t="n">
         <v>3768</v>
       </c>
-      <c r="P34" s="6" t="n"/>
-      <c r="Q34" s="6" t="n">
+      <c r="T34" s="5" t="n"/>
+      <c r="U34" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="R34" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" s="7" t="n"/>
-      <c r="T34" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U34" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V34" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="W34" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X34" s="7" t="n"/>
+      <c r="V34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" s="7" t="n"/>
+      <c r="X34" s="7" t="n">
+        <v>0</v>
+      </c>
       <c r="Y34" s="7" t="n">
         <v>0</v>
       </c>
       <c r="Z34" s="7" t="n">
         <v>0</v>
       </c>
-      <c r="AA34" s="7" t="n"/>
-      <c r="AB34" s="7" t="n">
+      <c r="AA34" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB34" s="7" t="n"/>
+      <c r="AC34" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD34" s="7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE34" s="7" t="n"/>
+      <c r="AF34" s="7" t="n">
         <v>778.1</v>
       </c>
-      <c r="AC34" s="4" t="inlineStr">
+      <c r="AG34" s="4" t="inlineStr">
         <is>
           <t>Soll n/a</t>
         </is>
@@ -3191,89 +3353,95 @@
           <t>32957282</t>
         </is>
       </c>
-      <c r="C35" s="12" t="inlineStr">
+      <c r="C35" s="12" t="n"/>
+      <c r="D35" s="12" t="n"/>
+      <c r="E35" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="F35" s="12" t="inlineStr"/>
+      <c r="G35" s="12" t="inlineStr">
         <is>
           <t>3782425</t>
         </is>
       </c>
-      <c r="D35" s="13" t="n">
+      <c r="H35" s="14" t="n">
         <v>45926</v>
       </c>
-      <c r="E35" s="12" t="inlineStr">
+      <c r="I35" s="12" t="inlineStr">
         <is>
           <t>Sika Supply Center GmbH</t>
         </is>
       </c>
-      <c r="F35" s="12" t="inlineStr">
+      <c r="J35" s="12" t="inlineStr">
         <is>
           <t>IE</t>
         </is>
       </c>
-      <c r="G35" s="12" t="inlineStr">
+      <c r="K35" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">DUB      </t>
         </is>
       </c>
-      <c r="H35" s="12" t="inlineStr">
+      <c r="L35" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">70499    </t>
         </is>
       </c>
-      <c r="I35" s="12" t="inlineStr">
+      <c r="M35" s="12" t="inlineStr">
         <is>
           <t>bis 2 Stpl</t>
         </is>
       </c>
-      <c r="J35" s="12" t="inlineStr">
+      <c r="N35" s="12" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="K35" s="12" t="inlineStr">
+      <c r="O35" s="12" t="inlineStr">
         <is>
           <t>EUR/Stpl</t>
         </is>
       </c>
-      <c r="L35" s="14" t="n">
+      <c r="P35" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="M35" s="15" t="n"/>
-      <c r="N35" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" s="14" t="n">
+      <c r="Q35" s="15" t="n"/>
+      <c r="R35" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" s="13" t="n">
         <v>22094</v>
       </c>
-      <c r="P35" s="14" t="n"/>
-      <c r="Q35" s="14" t="n"/>
-      <c r="R35" s="14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S35" s="15" t="n"/>
-      <c r="T35" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U35" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V35" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="W35" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X35" s="15" t="n"/>
+      <c r="T35" s="13" t="n"/>
+      <c r="U35" s="13" t="n"/>
+      <c r="V35" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" s="15" t="n"/>
+      <c r="X35" s="15" t="n">
+        <v>0</v>
+      </c>
       <c r="Y35" s="15" t="n">
         <v>0</v>
       </c>
       <c r="Z35" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="AA35" s="15" t="n"/>
-      <c r="AB35" s="15" t="n">
+      <c r="AA35" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB35" s="15" t="n"/>
+      <c r="AC35" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD35" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE35" s="15" t="n"/>
+      <c r="AF35" s="15" t="n">
         <v>3935.66</v>
       </c>
-      <c r="AC35" s="12" t="inlineStr">
+      <c r="AG35" s="12" t="inlineStr">
         <is>
           <t>Soll n/a</t>
         </is>
@@ -3281,12 +3449,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A19:AC19"/>
-    <mergeCell ref="A11:AC11"/>
-    <mergeCell ref="A1:AC1"/>
-    <mergeCell ref="A23:AC23"/>
-    <mergeCell ref="A3:AC3"/>
-    <mergeCell ref="A28:AC28"/>
+    <mergeCell ref="A1:AG1"/>
+    <mergeCell ref="A3:AG3"/>
+    <mergeCell ref="A19:AG19"/>
+    <mergeCell ref="A11:AG11"/>
+    <mergeCell ref="A28:AG28"/>
+    <mergeCell ref="A23:AG23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
